--- a/research/traditional_assets/database/data/belgium/belgium_apparel.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_apparel.xlsx
@@ -1169,7 +1169,7 @@
         <v>0.0851636633519009</v>
       </c>
       <c r="R2">
-        <v>0.07950864177571421</v>
+        <v>0.0795086417757141</v>
       </c>
       <c r="S2">
         <v>0.0433024624969006</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08549289583878675</v>
+        <v>0.08531291359918977</v>
       </c>
       <c r="C2">
-        <v>398.6403626181055</v>
+        <v>395.3287876951897</v>
       </c>
       <c r="D2">
-        <v>331.6403626181055</v>
+        <v>332.3277876951897</v>
       </c>
       <c r="E2">
-        <v>-10.6</v>
+        <v>-6.600999999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.999000000000001</v>
       </c>
       <c r="G2">
         <v>67</v>
@@ -1451,28 +1451,28 @@
         <v>42</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2011497</v>
       </c>
       <c r="N2">
-        <v>42</v>
+        <v>41.7988503</v>
       </c>
       <c r="O2">
-        <v>10.5</v>
+        <v>10.449712575</v>
       </c>
       <c r="P2">
-        <v>31.5</v>
+        <v>31.349137725</v>
       </c>
       <c r="Q2">
-        <v>43.4</v>
+        <v>43.249137725</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08549289583878675</v>
+        <v>0.08579359959514118</v>
       </c>
       <c r="T2">
-        <v>0.7736884202461267</v>
+        <v>0.7795496961570823</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>208.7997148392466</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08531291359918977</v>
+        <v>0.08513293135959282</v>
       </c>
       <c r="C3">
-        <v>395.3287876951897</v>
+        <v>392.0200684848722</v>
       </c>
       <c r="D3">
-        <v>332.3277876951897</v>
+        <v>333.0180684848722</v>
       </c>
       <c r="E3">
-        <v>-6.600999999999999</v>
+        <v>-2.601999999999999</v>
       </c>
       <c r="F3">
-        <v>3.999000000000001</v>
+        <v>7.998000000000001</v>
       </c>
       <c r="G3">
         <v>67</v>
@@ -1533,28 +1533,28 @@
         <v>42</v>
       </c>
       <c r="M3">
-        <v>0.2011497</v>
+        <v>0.4022994</v>
       </c>
       <c r="N3">
-        <v>41.7988503</v>
+        <v>41.5977006</v>
       </c>
       <c r="O3">
-        <v>10.449712575</v>
+        <v>10.39942515</v>
       </c>
       <c r="P3">
-        <v>31.349137725</v>
+        <v>31.19827545</v>
       </c>
       <c r="Q3">
-        <v>43.249137725</v>
+        <v>43.09827545</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08579359959514118</v>
+        <v>0.08610044016284982</v>
       </c>
       <c r="T3">
-        <v>0.7795496961570823</v>
+        <v>0.7855305899437716</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>208.7997148392466</v>
+        <v>104.3998574196233</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08513293135959282</v>
+        <v>0.08495294911999583</v>
       </c>
       <c r="C4">
-        <v>392.0200684848722</v>
+        <v>388.7142228190648</v>
       </c>
       <c r="D4">
-        <v>333.0180684848722</v>
+        <v>333.7112228190648</v>
       </c>
       <c r="E4">
-        <v>-2.601999999999999</v>
+        <v>1.397</v>
       </c>
       <c r="F4">
-        <v>7.998000000000001</v>
+        <v>11.997</v>
       </c>
       <c r="G4">
         <v>67</v>
@@ -1615,28 +1615,28 @@
         <v>42</v>
       </c>
       <c r="M4">
-        <v>0.4022994</v>
+        <v>0.6034491</v>
       </c>
       <c r="N4">
-        <v>41.5977006</v>
+        <v>41.3965509</v>
       </c>
       <c r="O4">
-        <v>10.39942515</v>
+        <v>10.349137725</v>
       </c>
       <c r="P4">
-        <v>31.19827545</v>
+        <v>31.047413175</v>
       </c>
       <c r="Q4">
-        <v>43.09827545</v>
+        <v>42.947413175</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08610044016284982</v>
+        <v>0.0864136073402019</v>
       </c>
       <c r="T4">
-        <v>0.7855305899437716</v>
+        <v>0.7916348011281245</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>104.3998574196233</v>
+        <v>69.59990494641553</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08495294911999583</v>
+        <v>0.08477296688039887</v>
       </c>
       <c r="C5">
-        <v>388.7142228190648</v>
+        <v>385.4112686784517</v>
       </c>
       <c r="D5">
-        <v>333.7112228190648</v>
+        <v>334.4072686784517</v>
       </c>
       <c r="E5">
-        <v>1.397</v>
+        <v>5.396000000000003</v>
       </c>
       <c r="F5">
-        <v>11.997</v>
+        <v>15.996</v>
       </c>
       <c r="G5">
         <v>67</v>
@@ -1697,28 +1697,28 @@
         <v>42</v>
       </c>
       <c r="M5">
-        <v>0.6034491</v>
+        <v>0.8045988000000001</v>
       </c>
       <c r="N5">
-        <v>41.3965509</v>
+        <v>41.1954012</v>
       </c>
       <c r="O5">
-        <v>10.349137725</v>
+        <v>10.2988503</v>
       </c>
       <c r="P5">
-        <v>31.047413175</v>
+        <v>30.8965509</v>
       </c>
       <c r="Q5">
-        <v>42.947413175</v>
+        <v>42.7965509</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0864136073402019</v>
+        <v>0.08673329883374883</v>
       </c>
       <c r="T5">
-        <v>0.7916348011281245</v>
+        <v>0.7978661833788182</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>69.59990494641553</v>
+        <v>52.19992870981164</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08477296688039887</v>
+        <v>0.08459298464080192</v>
       </c>
       <c r="C6">
-        <v>385.4112686784517</v>
+        <v>382.1112241940457</v>
       </c>
       <c r="D6">
-        <v>334.4072686784517</v>
+        <v>335.1062241940457</v>
       </c>
       <c r="E6">
-        <v>5.396000000000003</v>
+        <v>9.395000000000005</v>
       </c>
       <c r="F6">
-        <v>15.996</v>
+        <v>19.995</v>
       </c>
       <c r="G6">
         <v>67</v>
@@ -1779,28 +1779,28 @@
         <v>42</v>
       </c>
       <c r="M6">
-        <v>0.8045988000000001</v>
+        <v>1.0057485</v>
       </c>
       <c r="N6">
-        <v>41.1954012</v>
+        <v>40.9942515</v>
       </c>
       <c r="O6">
-        <v>10.2988503</v>
+        <v>10.248562875</v>
       </c>
       <c r="P6">
-        <v>30.8965509</v>
+        <v>30.745688625</v>
       </c>
       <c r="Q6">
-        <v>42.7965509</v>
+        <v>42.645688625</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08673329883374883</v>
+        <v>0.08705972067452833</v>
       </c>
       <c r="T6">
-        <v>0.7978661833788182</v>
+        <v>0.8042287526242633</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>52.19992870981164</v>
+        <v>41.75994296784931</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08459298464080192</v>
+        <v>0.08441300240120495</v>
       </c>
       <c r="C7">
-        <v>382.1112241940457</v>
+        <v>378.8141076487622</v>
       </c>
       <c r="D7">
-        <v>335.1062241940457</v>
+        <v>335.8081076487622</v>
       </c>
       <c r="E7">
-        <v>9.395000000000005</v>
+        <v>13.394</v>
       </c>
       <c r="F7">
-        <v>19.995</v>
+        <v>23.994</v>
       </c>
       <c r="G7">
         <v>67</v>
@@ -1861,28 +1861,28 @@
         <v>42</v>
       </c>
       <c r="M7">
-        <v>1.0057485</v>
+        <v>1.2068982</v>
       </c>
       <c r="N7">
-        <v>40.9942515</v>
+        <v>40.7931018</v>
       </c>
       <c r="O7">
-        <v>10.248562875</v>
+        <v>10.19827545</v>
       </c>
       <c r="P7">
-        <v>30.745688625</v>
+        <v>30.59482635</v>
       </c>
       <c r="Q7">
-        <v>42.645688625</v>
+        <v>42.49482635</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08705972067452833</v>
+        <v>0.08739308766085632</v>
       </c>
       <c r="T7">
-        <v>0.8042287526242633</v>
+        <v>0.8107266956834412</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>41.75994296784931</v>
+        <v>34.79995247320776</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08441300240120495</v>
+        <v>0.08423302016160798</v>
       </c>
       <c r="C8">
-        <v>378.8141076487622</v>
+        <v>375.5199374790126</v>
       </c>
       <c r="D8">
-        <v>335.8081076487622</v>
+        <v>336.5129374790126</v>
       </c>
       <c r="E8">
-        <v>13.394</v>
+        <v>17.393</v>
       </c>
       <c r="F8">
-        <v>23.994</v>
+        <v>27.993</v>
       </c>
       <c r="G8">
         <v>67</v>
@@ -1943,28 +1943,28 @@
         <v>42</v>
       </c>
       <c r="M8">
-        <v>1.2068982</v>
+        <v>1.4080479</v>
       </c>
       <c r="N8">
-        <v>40.7931018</v>
+        <v>40.5919521</v>
       </c>
       <c r="O8">
-        <v>10.19827545</v>
+        <v>10.147988025</v>
       </c>
       <c r="P8">
-        <v>30.59482635</v>
+        <v>30.443964075</v>
       </c>
       <c r="Q8">
-        <v>42.49482635</v>
+        <v>42.343964075</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08739308766085632</v>
+        <v>0.087733623829686</v>
       </c>
       <c r="T8">
-        <v>0.8107266956834412</v>
+        <v>0.8173643794535693</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.79995247320777</v>
+        <v>29.82853069132094</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08423302016160797</v>
+        <v>0.08405303792201102</v>
       </c>
       <c r="C9">
-        <v>375.5199374790126</v>
+        <v>372.2287322763193</v>
       </c>
       <c r="D9">
-        <v>336.5129374790126</v>
+        <v>337.2207322763193</v>
       </c>
       <c r="E9">
-        <v>17.39300000000001</v>
+        <v>21.392</v>
       </c>
       <c r="F9">
-        <v>27.99300000000001</v>
+        <v>31.992</v>
       </c>
       <c r="G9">
         <v>67</v>
@@ -2025,28 +2025,28 @@
         <v>42</v>
       </c>
       <c r="M9">
-        <v>1.4080479</v>
+        <v>1.6091976</v>
       </c>
       <c r="N9">
-        <v>40.5919521</v>
+        <v>40.3908024</v>
       </c>
       <c r="O9">
-        <v>10.147988025</v>
+        <v>10.0977006</v>
       </c>
       <c r="P9">
-        <v>30.443964075</v>
+        <v>30.2931018</v>
       </c>
       <c r="Q9">
-        <v>42.343964075</v>
+        <v>42.1931018</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.087733623829686</v>
+        <v>0.08808156295870762</v>
       </c>
       <c r="T9">
-        <v>0.8173643794535693</v>
+        <v>0.8241463606969611</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.82853069132094</v>
+        <v>26.09996435490582</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08405303792201102</v>
+        <v>0.08387305568241406</v>
       </c>
       <c r="C10">
-        <v>372.2287322763193</v>
+        <v>368.9405107889504</v>
       </c>
       <c r="D10">
-        <v>337.2207322763193</v>
+        <v>337.9315107889504</v>
       </c>
       <c r="E10">
-        <v>21.392</v>
+        <v>25.391</v>
       </c>
       <c r="F10">
-        <v>31.992</v>
+        <v>35.991</v>
       </c>
       <c r="G10">
         <v>67</v>
@@ -2107,28 +2107,28 @@
         <v>42</v>
       </c>
       <c r="M10">
-        <v>1.6091976</v>
+        <v>1.8103473</v>
       </c>
       <c r="N10">
-        <v>40.3908024</v>
+        <v>40.1896527</v>
       </c>
       <c r="O10">
-        <v>10.0977006</v>
+        <v>10.047413175</v>
       </c>
       <c r="P10">
-        <v>30.2931018</v>
+        <v>30.142239525</v>
       </c>
       <c r="Q10">
-        <v>42.1931018</v>
+        <v>42.042239525</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08808156295870762</v>
+        <v>0.0884371491015539</v>
       </c>
       <c r="T10">
-        <v>0.8241463606969611</v>
+        <v>0.8310773964731746</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>26.09996435490582</v>
+        <v>23.19996831547185</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08387305568241406</v>
+        <v>0.08369307344281707</v>
       </c>
       <c r="C11">
-        <v>368.9405107889504</v>
+        <v>365.6552919235746</v>
       </c>
       <c r="D11">
-        <v>337.9315107889504</v>
+        <v>338.6452919235746</v>
       </c>
       <c r="E11">
-        <v>25.391</v>
+        <v>29.39</v>
       </c>
       <c r="F11">
-        <v>35.991</v>
+        <v>39.99</v>
       </c>
       <c r="G11">
         <v>67</v>
@@ -2189,28 +2189,28 @@
         <v>42</v>
       </c>
       <c r="M11">
-        <v>1.8103473</v>
+        <v>2.011497</v>
       </c>
       <c r="N11">
-        <v>40.1896527</v>
+        <v>39.988503</v>
       </c>
       <c r="O11">
-        <v>10.047413175</v>
+        <v>9.99712575</v>
       </c>
       <c r="P11">
-        <v>30.142239525</v>
+        <v>29.99137725</v>
       </c>
       <c r="Q11">
-        <v>42.042239525</v>
+        <v>41.89137725</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0884371491015539</v>
+        <v>0.08880063715868564</v>
       </c>
       <c r="T11">
-        <v>0.8310773964731746</v>
+        <v>0.8381624552666372</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.19996831547185</v>
+        <v>20.87997148392466</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08369307344281707</v>
+        <v>0.08351309120322011</v>
       </c>
       <c r="C12">
-        <v>365.6552919235746</v>
+        <v>362.3730947469377</v>
       </c>
       <c r="D12">
-        <v>338.6452919235746</v>
+        <v>339.3620947469377</v>
       </c>
       <c r="E12">
-        <v>29.39000000000001</v>
+        <v>33.389</v>
       </c>
       <c r="F12">
-        <v>39.99000000000001</v>
+        <v>43.989</v>
       </c>
       <c r="G12">
         <v>67</v>
@@ -2271,28 +2271,28 @@
         <v>42</v>
       </c>
       <c r="M12">
-        <v>2.011497</v>
+        <v>2.2126467</v>
       </c>
       <c r="N12">
-        <v>39.988503</v>
+        <v>39.7873533</v>
       </c>
       <c r="O12">
-        <v>9.99712575</v>
+        <v>9.946838325</v>
       </c>
       <c r="P12">
-        <v>29.99137725</v>
+        <v>29.840514975</v>
       </c>
       <c r="Q12">
-        <v>41.89137725</v>
+        <v>41.740514975</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08880063715868564</v>
+        <v>0.08917229348676417</v>
       </c>
       <c r="T12">
-        <v>0.8381624552666372</v>
+        <v>0.8454067288644475</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.87997148392466</v>
+        <v>18.98179225811333</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08351309120322011</v>
+        <v>0.08333310896362314</v>
       </c>
       <c r="C13">
-        <v>362.3730947469377</v>
+        <v>359.0939384875608</v>
       </c>
       <c r="D13">
-        <v>339.3620947469377</v>
+        <v>340.0819384875608</v>
       </c>
       <c r="E13">
-        <v>33.389</v>
+        <v>37.388</v>
       </c>
       <c r="F13">
-        <v>43.989</v>
+        <v>47.988</v>
       </c>
       <c r="G13">
         <v>67</v>
@@ -2353,28 +2353,28 @@
         <v>42</v>
       </c>
       <c r="M13">
-        <v>2.2126467</v>
+        <v>2.4137964</v>
       </c>
       <c r="N13">
-        <v>39.7873533</v>
+        <v>39.5862036</v>
       </c>
       <c r="O13">
-        <v>9.946838325</v>
+        <v>9.896550899999999</v>
       </c>
       <c r="P13">
-        <v>29.840514975</v>
+        <v>29.6896527</v>
       </c>
       <c r="Q13">
-        <v>41.740514975</v>
+        <v>41.58965269999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08917229348676417</v>
+        <v>0.08955239654957176</v>
       </c>
       <c r="T13">
-        <v>0.8454067288644475</v>
+        <v>0.8528156450440261</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.98179225811333</v>
+        <v>17.39997623660388</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08333310896362314</v>
+        <v>0.08315312672402618</v>
       </c>
       <c r="C14">
-        <v>359.0939384875608</v>
+        <v>355.8178425374594</v>
       </c>
       <c r="D14">
-        <v>340.0819384875608</v>
+        <v>340.8048425374594</v>
       </c>
       <c r="E14">
-        <v>37.388</v>
+        <v>41.38700000000001</v>
       </c>
       <c r="F14">
-        <v>47.988</v>
+        <v>51.98700000000001</v>
       </c>
       <c r="G14">
         <v>67</v>
@@ -2435,28 +2435,28 @@
         <v>42</v>
       </c>
       <c r="M14">
-        <v>2.4137964</v>
+        <v>2.6149461</v>
       </c>
       <c r="N14">
-        <v>39.5862036</v>
+        <v>39.3850539</v>
       </c>
       <c r="O14">
-        <v>9.896550899999999</v>
+        <v>9.846263475000001</v>
       </c>
       <c r="P14">
-        <v>29.6896527</v>
+        <v>29.538790425</v>
       </c>
       <c r="Q14">
-        <v>41.58965269999999</v>
+        <v>41.438790425</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08955239654957176</v>
+        <v>0.08994123761382319</v>
       </c>
       <c r="T14">
-        <v>0.8528156450440261</v>
+        <v>0.8603948811357788</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.39997623660388</v>
+        <v>16.06151652609589</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08315312672402618</v>
+        <v>0.08297314448442919</v>
       </c>
       <c r="C15">
-        <v>355.8178425374594</v>
+        <v>352.5448264538849</v>
       </c>
       <c r="D15">
-        <v>340.8048425374594</v>
+        <v>341.5308264538849</v>
       </c>
       <c r="E15">
-        <v>41.38700000000001</v>
+        <v>45.38600000000001</v>
       </c>
       <c r="F15">
-        <v>51.98700000000001</v>
+        <v>55.98600000000001</v>
       </c>
       <c r="G15">
         <v>67</v>
@@ -2517,28 +2517,28 @@
         <v>42</v>
       </c>
       <c r="M15">
-        <v>2.6149461</v>
+        <v>2.8160958</v>
       </c>
       <c r="N15">
-        <v>39.3850539</v>
+        <v>39.1839042</v>
       </c>
       <c r="O15">
-        <v>9.846263475000001</v>
+        <v>9.79597605</v>
       </c>
       <c r="P15">
-        <v>29.538790425</v>
+        <v>29.38792815</v>
       </c>
       <c r="Q15">
-        <v>41.438790425</v>
+        <v>41.28792815</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08994123761382319</v>
+        <v>0.09033912149352233</v>
       </c>
       <c r="T15">
-        <v>0.8603948811357788</v>
+        <v>0.8681503785319911</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.06151652609589</v>
+        <v>14.91426534566047</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08297314448442919</v>
+        <v>0.08279316224483224</v>
       </c>
       <c r="C16">
-        <v>352.5448264538849</v>
+        <v>349.2749099610878</v>
       </c>
       <c r="D16">
-        <v>341.5308264538849</v>
+        <v>342.2599099610878</v>
       </c>
       <c r="E16">
-        <v>45.38600000000001</v>
+        <v>49.38500000000001</v>
       </c>
       <c r="F16">
-        <v>55.98600000000001</v>
+        <v>59.98500000000001</v>
       </c>
       <c r="G16">
         <v>67</v>
@@ -2599,28 +2599,28 @@
         <v>42</v>
       </c>
       <c r="M16">
-        <v>2.8160958</v>
+        <v>3.0172455</v>
       </c>
       <c r="N16">
-        <v>39.1839042</v>
+        <v>38.9827545</v>
       </c>
       <c r="O16">
-        <v>9.79597605</v>
+        <v>9.745688625</v>
       </c>
       <c r="P16">
-        <v>29.38792815</v>
+        <v>29.237065875</v>
       </c>
       <c r="Q16">
-        <v>41.28792815</v>
+        <v>41.137065875</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09033912149352233</v>
+        <v>0.09074636734686145</v>
       </c>
       <c r="T16">
-        <v>0.8681503785319911</v>
+        <v>0.8760883582198787</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.91426534566047</v>
+        <v>13.9199809892831</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08279316224483224</v>
+        <v>0.08261318000523528</v>
       </c>
       <c r="C17">
-        <v>349.2749099610878</v>
+        <v>346.0081129521049</v>
       </c>
       <c r="D17">
-        <v>342.2599099610878</v>
+        <v>342.9921129521048</v>
       </c>
       <c r="E17">
-        <v>49.385</v>
+        <v>53.38400000000001</v>
       </c>
       <c r="F17">
-        <v>59.985</v>
+        <v>63.98400000000001</v>
       </c>
       <c r="G17">
         <v>67</v>
@@ -2681,28 +2681,28 @@
         <v>42</v>
       </c>
       <c r="M17">
-        <v>3.0172455</v>
+        <v>3.2183952</v>
       </c>
       <c r="N17">
-        <v>38.9827545</v>
+        <v>38.7816048</v>
       </c>
       <c r="O17">
-        <v>9.745688625</v>
+        <v>9.695401199999999</v>
       </c>
       <c r="P17">
-        <v>29.237065875</v>
+        <v>29.0862036</v>
       </c>
       <c r="Q17">
-        <v>41.137065875</v>
+        <v>40.9862036</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09074636734686145</v>
+        <v>0.09116330953004199</v>
       </c>
       <c r="T17">
-        <v>0.8760883582198787</v>
+        <v>0.8842153374241448</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.91998098928311</v>
+        <v>13.04998217745291</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08261318000523528</v>
+        <v>0.08262444776563831</v>
       </c>
       <c r="C18">
-        <v>346.0081129521049</v>
+        <v>341.9631815830365</v>
       </c>
       <c r="D18">
-        <v>342.9921129521048</v>
+        <v>342.9461815830365</v>
       </c>
       <c r="E18">
-        <v>53.38400000000001</v>
+        <v>57.383</v>
       </c>
       <c r="F18">
-        <v>63.98400000000001</v>
+        <v>67.983</v>
       </c>
       <c r="G18">
         <v>67</v>
@@ -2763,45 +2763,45 @@
         <v>42</v>
       </c>
       <c r="M18">
-        <v>3.2183952</v>
+        <v>3.5215194</v>
       </c>
       <c r="N18">
-        <v>38.7816048</v>
+        <v>38.4784806</v>
       </c>
       <c r="O18">
-        <v>9.695401199999999</v>
+        <v>9.619620149999999</v>
       </c>
       <c r="P18">
-        <v>29.0862036</v>
+        <v>28.85886045</v>
       </c>
       <c r="Q18">
-        <v>40.9862036</v>
+        <v>40.75886045</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09116330953004199</v>
+        <v>0.09159029851281725</v>
       </c>
       <c r="T18">
-        <v>0.8842153374241448</v>
+        <v>0.8925381474526102</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>13.04998217745291</v>
+        <v>11.92667006179208</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08262444776563831</v>
+        <v>0.08245571552604133</v>
       </c>
       <c r="C19">
-        <v>341.9631815830365</v>
+        <v>338.6532835251715</v>
       </c>
       <c r="D19">
-        <v>342.9461815830365</v>
+        <v>343.6352835251715</v>
       </c>
       <c r="E19">
-        <v>57.383</v>
+        <v>61.38200000000001</v>
       </c>
       <c r="F19">
-        <v>67.983</v>
+        <v>71.98200000000001</v>
       </c>
       <c r="G19">
         <v>67</v>
@@ -2845,28 +2845,28 @@
         <v>42</v>
       </c>
       <c r="M19">
-        <v>3.5215194</v>
+        <v>3.728667600000001</v>
       </c>
       <c r="N19">
-        <v>38.4784806</v>
+        <v>38.2713324</v>
       </c>
       <c r="O19">
-        <v>9.619620149999999</v>
+        <v>9.5678331</v>
       </c>
       <c r="P19">
-        <v>28.85886045</v>
+        <v>28.7034993</v>
       </c>
       <c r="Q19">
-        <v>40.75886045</v>
+        <v>40.6034993</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09159029851281725</v>
+        <v>0.09202770186102602</v>
       </c>
       <c r="T19">
-        <v>0.8925381474526102</v>
+        <v>0.9010639528476231</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.92667006179208</v>
+        <v>11.26407728058141</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08245571552604133</v>
+        <v>0.08228698328644438</v>
       </c>
       <c r="C20">
-        <v>338.6532835251716</v>
+        <v>335.3461603492003</v>
       </c>
       <c r="D20">
-        <v>343.6352835251715</v>
+        <v>344.3271603492003</v>
       </c>
       <c r="E20">
-        <v>61.382</v>
+        <v>65.38100000000001</v>
       </c>
       <c r="F20">
-        <v>71.982</v>
+        <v>75.98100000000001</v>
       </c>
       <c r="G20">
         <v>67</v>
@@ -2927,28 +2927,28 @@
         <v>42</v>
       </c>
       <c r="M20">
-        <v>3.7286676</v>
+        <v>3.9358158</v>
       </c>
       <c r="N20">
-        <v>38.2713324</v>
+        <v>38.0641842</v>
       </c>
       <c r="O20">
-        <v>9.5678331</v>
+        <v>9.51604605</v>
       </c>
       <c r="P20">
-        <v>28.7034993</v>
+        <v>28.54813815</v>
       </c>
       <c r="Q20">
-        <v>40.6034993</v>
+        <v>40.44813815</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09202770186102602</v>
+        <v>0.09247590529190663</v>
       </c>
       <c r="T20">
-        <v>0.9010639528476231</v>
+        <v>0.9098002719560936</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.26407728058141</v>
+        <v>10.67123110791923</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08228698328644438</v>
+        <v>0.08211825104684742</v>
       </c>
       <c r="C21">
-        <v>335.3461603492003</v>
+        <v>332.0418288498163</v>
       </c>
       <c r="D21">
-        <v>344.3271603492003</v>
+        <v>345.0218288498163</v>
       </c>
       <c r="E21">
-        <v>65.38100000000001</v>
+        <v>69.38000000000002</v>
       </c>
       <c r="F21">
-        <v>75.98100000000001</v>
+        <v>79.98000000000002</v>
       </c>
       <c r="G21">
         <v>67</v>
@@ -3009,28 +3009,28 @@
         <v>42</v>
       </c>
       <c r="M21">
-        <v>3.9358158</v>
+        <v>4.142964000000001</v>
       </c>
       <c r="N21">
-        <v>38.0641842</v>
+        <v>37.857036</v>
       </c>
       <c r="O21">
-        <v>9.51604605</v>
+        <v>9.464259</v>
       </c>
       <c r="P21">
-        <v>28.54813815</v>
+        <v>28.392777</v>
       </c>
       <c r="Q21">
-        <v>40.44813815</v>
+        <v>40.292777</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09247590529190663</v>
+        <v>0.09293531380855927</v>
       </c>
       <c r="T21">
-        <v>0.9098002719560936</v>
+        <v>0.9187549990422754</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.67123110791923</v>
+        <v>10.13766955252326</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08211825104684742</v>
+        <v>0.08221726880725044</v>
       </c>
       <c r="C22">
-        <v>332.0418288498163</v>
+        <v>327.6348345815053</v>
       </c>
       <c r="D22">
-        <v>345.0218288498163</v>
+        <v>344.6138345815053</v>
       </c>
       <c r="E22">
-        <v>69.38000000000002</v>
+        <v>73.37900000000002</v>
       </c>
       <c r="F22">
-        <v>79.98000000000002</v>
+        <v>83.97900000000001</v>
       </c>
       <c r="G22">
         <v>67</v>
@@ -3091,45 +3091,45 @@
         <v>42</v>
       </c>
       <c r="M22">
-        <v>4.142964000000001</v>
+        <v>4.4928765</v>
       </c>
       <c r="N22">
-        <v>37.857036</v>
+        <v>37.5071235</v>
       </c>
       <c r="O22">
-        <v>9.464259</v>
+        <v>9.376780875</v>
       </c>
       <c r="P22">
-        <v>28.392777</v>
+        <v>28.130342625</v>
       </c>
       <c r="Q22">
-        <v>40.292777</v>
+        <v>40.030342625</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09293531380855927</v>
+        <v>0.09340635292057017</v>
       </c>
       <c r="T22">
-        <v>0.9187549990422754</v>
+        <v>0.9279364280800064</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>10.13766955252326</v>
+        <v>9.348131425379709</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08221726880725044</v>
+        <v>0.08206128656765348</v>
       </c>
       <c r="C23">
-        <v>327.6348345815053</v>
+        <v>324.2789841968475</v>
       </c>
       <c r="D23">
-        <v>344.6138345815053</v>
+        <v>345.2569841968475</v>
       </c>
       <c r="E23">
-        <v>73.379</v>
+        <v>77.37800000000001</v>
       </c>
       <c r="F23">
-        <v>83.979</v>
+        <v>87.97800000000001</v>
       </c>
       <c r="G23">
         <v>67</v>
@@ -3173,28 +3173,28 @@
         <v>42</v>
       </c>
       <c r="M23">
-        <v>4.492876499999999</v>
+        <v>4.706823</v>
       </c>
       <c r="N23">
-        <v>37.5071235</v>
+        <v>37.293177</v>
       </c>
       <c r="O23">
-        <v>9.376780875</v>
+        <v>9.32329425</v>
       </c>
       <c r="P23">
-        <v>28.130342625</v>
+        <v>27.96988275</v>
       </c>
       <c r="Q23">
-        <v>40.030342625</v>
+        <v>39.86988275</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09340635292057017</v>
+        <v>0.09388946995853009</v>
       </c>
       <c r="T23">
-        <v>0.9279364280800064</v>
+        <v>0.937353278375115</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.348131425379711</v>
+        <v>8.923216360589723</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08206128656765348</v>
+        <v>0.08190530432805651</v>
       </c>
       <c r="C24">
-        <v>324.2789841968475</v>
+        <v>320.9255389091692</v>
       </c>
       <c r="D24">
-        <v>345.2569841968475</v>
+        <v>345.9025389091692</v>
       </c>
       <c r="E24">
-        <v>77.37800000000001</v>
+        <v>81.37700000000002</v>
       </c>
       <c r="F24">
-        <v>87.97800000000001</v>
+        <v>91.97700000000002</v>
       </c>
       <c r="G24">
         <v>67</v>
@@ -3255,28 +3255,28 @@
         <v>42</v>
       </c>
       <c r="M24">
-        <v>4.706823</v>
+        <v>4.9207695</v>
       </c>
       <c r="N24">
-        <v>37.293177</v>
+        <v>37.0792305</v>
       </c>
       <c r="O24">
-        <v>9.32329425</v>
+        <v>9.269807625</v>
       </c>
       <c r="P24">
-        <v>27.96988275</v>
+        <v>27.809422875</v>
       </c>
       <c r="Q24">
-        <v>39.86988275</v>
+        <v>39.709422875</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09388946995853009</v>
+        <v>0.09438513549098247</v>
       </c>
       <c r="T24">
-        <v>0.937353278375115</v>
+        <v>0.9470147221843823</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.923216360589723</v>
+        <v>8.53525043186843</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08190530432805651</v>
+        <v>0.08174932208845954</v>
       </c>
       <c r="C25">
-        <v>320.9255389091692</v>
+        <v>317.5745122347518</v>
       </c>
       <c r="D25">
-        <v>345.9025389091692</v>
+        <v>346.5505122347517</v>
       </c>
       <c r="E25">
-        <v>81.37700000000002</v>
+        <v>85.37600000000002</v>
       </c>
       <c r="F25">
-        <v>91.97700000000002</v>
+        <v>95.97600000000001</v>
       </c>
       <c r="G25">
         <v>67</v>
@@ -3337,28 +3337,28 @@
         <v>42</v>
       </c>
       <c r="M25">
-        <v>4.9207695</v>
+        <v>5.134716000000001</v>
       </c>
       <c r="N25">
-        <v>37.0792305</v>
+        <v>36.865284</v>
       </c>
       <c r="O25">
-        <v>9.269807625</v>
+        <v>9.216321000000001</v>
       </c>
       <c r="P25">
-        <v>27.809422875</v>
+        <v>27.648963</v>
       </c>
       <c r="Q25">
-        <v>39.709422875</v>
+        <v>39.548963</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09438513549098247</v>
+        <v>0.09489384485323624</v>
       </c>
       <c r="T25">
-        <v>0.9470147221843823</v>
+        <v>0.9569304145149462</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.53525043186843</v>
+        <v>8.179614997207246</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08174932208845954</v>
+        <v>0.08159333984886259</v>
       </c>
       <c r="C26">
-        <v>317.5745122347518</v>
+        <v>314.2259177913459</v>
       </c>
       <c r="D26">
-        <v>346.5505122347517</v>
+        <v>347.2009177913459</v>
       </c>
       <c r="E26">
-        <v>85.376</v>
+        <v>89.37500000000001</v>
       </c>
       <c r="F26">
-        <v>95.976</v>
+        <v>99.97500000000001</v>
       </c>
       <c r="G26">
         <v>67</v>
@@ -3419,28 +3419,28 @@
         <v>42</v>
       </c>
       <c r="M26">
-        <v>5.134716</v>
+        <v>5.348662500000001</v>
       </c>
       <c r="N26">
-        <v>36.865284</v>
+        <v>36.6513375</v>
       </c>
       <c r="O26">
-        <v>9.216321000000001</v>
+        <v>9.162834374999999</v>
       </c>
       <c r="P26">
-        <v>27.648963</v>
+        <v>27.488503125</v>
       </c>
       <c r="Q26">
-        <v>39.548963</v>
+        <v>39.388503125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09489384485323624</v>
+        <v>0.09541611979848344</v>
       </c>
       <c r="T26">
-        <v>0.9569304145149462</v>
+        <v>0.9671105253076584</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.179614997207246</v>
+        <v>7.852430397318955</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08159333984886259</v>
+        <v>0.08159335760926562</v>
       </c>
       <c r="C27">
-        <v>314.2259177913459</v>
+        <v>310.2268435960905</v>
       </c>
       <c r="D27">
-        <v>347.2009177913459</v>
+        <v>347.2008435960905</v>
       </c>
       <c r="E27">
-        <v>89.37500000000001</v>
+        <v>93.37400000000002</v>
       </c>
       <c r="F27">
-        <v>99.97500000000001</v>
+        <v>103.974</v>
       </c>
       <c r="G27">
         <v>67</v>
@@ -3501,45 +3501,45 @@
         <v>42</v>
       </c>
       <c r="M27">
-        <v>5.348662500000001</v>
+        <v>5.645788200000001</v>
       </c>
       <c r="N27">
-        <v>36.6513375</v>
+        <v>36.3542118</v>
       </c>
       <c r="O27">
-        <v>9.162834374999999</v>
+        <v>9.08855295</v>
       </c>
       <c r="P27">
-        <v>27.488503125</v>
+        <v>27.26565885</v>
       </c>
       <c r="Q27">
-        <v>39.388503125</v>
+        <v>39.16565885</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09541611979848344</v>
+        <v>0.09595251028279136</v>
       </c>
       <c r="T27">
-        <v>0.9671105253076584</v>
+        <v>0.9775657742299034</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.852430397318955</v>
+        <v>7.439173860613474</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08159335760926562</v>
+        <v>0.08144337536966864</v>
       </c>
       <c r="C28">
-        <v>310.2268435960905</v>
+        <v>306.855536902797</v>
       </c>
       <c r="D28">
-        <v>347.2008435960905</v>
+        <v>347.828536902797</v>
       </c>
       <c r="E28">
-        <v>93.37400000000002</v>
+        <v>97.37300000000002</v>
       </c>
       <c r="F28">
-        <v>103.974</v>
+        <v>107.973</v>
       </c>
       <c r="G28">
         <v>67</v>
@@ -3583,28 +3583,28 @@
         <v>42</v>
       </c>
       <c r="M28">
-        <v>5.645788200000001</v>
+        <v>5.862933900000001</v>
       </c>
       <c r="N28">
-        <v>36.3542118</v>
+        <v>36.1370661</v>
       </c>
       <c r="O28">
-        <v>9.08855295</v>
+        <v>9.034266525</v>
       </c>
       <c r="P28">
-        <v>27.26565885</v>
+        <v>27.102799575</v>
       </c>
       <c r="Q28">
-        <v>39.16565885</v>
+        <v>39.002799575</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09595251028279136</v>
+        <v>0.09650359639680636</v>
       </c>
       <c r="T28">
-        <v>0.9775657742299034</v>
+        <v>0.9883074683281003</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.439173860613474</v>
+        <v>7.163648902812975</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08144337536966864</v>
+        <v>0.08129339313007167</v>
       </c>
       <c r="C29">
-        <v>306.855536902797</v>
+        <v>303.4865038933531</v>
       </c>
       <c r="D29">
-        <v>347.828536902797</v>
+        <v>348.4585038933532</v>
       </c>
       <c r="E29">
-        <v>97.37300000000002</v>
+        <v>101.372</v>
       </c>
       <c r="F29">
-        <v>107.973</v>
+        <v>111.972</v>
       </c>
       <c r="G29">
         <v>67</v>
@@ -3665,28 +3665,28 @@
         <v>42</v>
       </c>
       <c r="M29">
-        <v>5.862933900000001</v>
+        <v>6.080079600000001</v>
       </c>
       <c r="N29">
-        <v>36.1370661</v>
+        <v>35.9199204</v>
       </c>
       <c r="O29">
-        <v>9.034266525</v>
+        <v>8.979980099999999</v>
       </c>
       <c r="P29">
-        <v>27.102799575</v>
+        <v>26.9399403</v>
       </c>
       <c r="Q29">
-        <v>39.002799575</v>
+        <v>38.83994029999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09650359639680636</v>
+        <v>0.09706999045843288</v>
       </c>
       <c r="T29">
-        <v>0.9883074683281003</v>
+        <v>0.9993475428179137</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.163648902812975</v>
+        <v>6.907804299141081</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08129339313007167</v>
+        <v>0.08114341089047469</v>
       </c>
       <c r="C30">
-        <v>303.4865038933531</v>
+        <v>300.1197569440698</v>
       </c>
       <c r="D30">
-        <v>348.4585038933532</v>
+        <v>349.0907569440698</v>
       </c>
       <c r="E30">
-        <v>101.372</v>
+        <v>105.371</v>
       </c>
       <c r="F30">
-        <v>111.972</v>
+        <v>115.971</v>
       </c>
       <c r="G30">
         <v>67</v>
@@ -3747,28 +3747,28 @@
         <v>42</v>
       </c>
       <c r="M30">
-        <v>6.080079600000001</v>
+        <v>6.297225300000001</v>
       </c>
       <c r="N30">
-        <v>35.9199204</v>
+        <v>35.7027747</v>
       </c>
       <c r="O30">
-        <v>8.979980099999999</v>
+        <v>8.925693675</v>
       </c>
       <c r="P30">
-        <v>26.9399403</v>
+        <v>26.777081025</v>
       </c>
       <c r="Q30">
-        <v>38.83994029999999</v>
+        <v>38.677081025</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09706999045843288</v>
+        <v>0.09765233928235874</v>
       </c>
       <c r="T30">
-        <v>0.9993475428179137</v>
+        <v>1.010698605321525</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.907804299141081</v>
+        <v>6.669604150894838</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08114341089047469</v>
+        <v>0.08099342865087775</v>
       </c>
       <c r="C31">
-        <v>300.1197569440698</v>
+        <v>296.7553085212439</v>
       </c>
       <c r="D31">
-        <v>349.0907569440698</v>
+        <v>349.7253085212439</v>
       </c>
       <c r="E31">
-        <v>105.371</v>
+        <v>109.37</v>
       </c>
       <c r="F31">
-        <v>115.971</v>
+        <v>119.97</v>
       </c>
       <c r="G31">
         <v>67</v>
@@ -3829,28 +3829,28 @@
         <v>42</v>
       </c>
       <c r="M31">
-        <v>6.2972253</v>
+        <v>6.514371</v>
       </c>
       <c r="N31">
-        <v>35.7027747</v>
+        <v>35.485629</v>
       </c>
       <c r="O31">
-        <v>8.925693675</v>
+        <v>8.871407250000001</v>
       </c>
       <c r="P31">
-        <v>26.777081025</v>
+        <v>26.61422175</v>
       </c>
       <c r="Q31">
-        <v>38.677081025</v>
+        <v>38.51422175</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09765233928235874</v>
+        <v>0.09825132664411106</v>
       </c>
       <c r="T31">
-        <v>1.010698605321525</v>
+        <v>1.022373983896667</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.669604150894839</v>
+        <v>6.447284012531679</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08099342865087775</v>
+        <v>0.08084344641128076</v>
       </c>
       <c r="C32">
-        <v>296.7553085212439</v>
+        <v>293.39317118198</v>
       </c>
       <c r="D32">
-        <v>349.7253085212439</v>
+        <v>350.36217118198</v>
       </c>
       <c r="E32">
-        <v>109.37</v>
+        <v>113.369</v>
       </c>
       <c r="F32">
-        <v>119.97</v>
+        <v>123.969</v>
       </c>
       <c r="G32">
         <v>67</v>
@@ -3911,28 +3911,28 @@
         <v>42</v>
       </c>
       <c r="M32">
-        <v>6.514371</v>
+        <v>6.7315167</v>
       </c>
       <c r="N32">
-        <v>35.485629</v>
+        <v>35.2684833</v>
       </c>
       <c r="O32">
-        <v>8.871407250000001</v>
+        <v>8.817120825</v>
       </c>
       <c r="P32">
-        <v>26.61422175</v>
+        <v>26.451362475</v>
       </c>
       <c r="Q32">
-        <v>38.51422175</v>
+        <v>38.351362475</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09825132664411106</v>
+        <v>0.09886767595837792</v>
       </c>
       <c r="T32">
-        <v>1.022373983896667</v>
+        <v>1.034387779242104</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.447284012531679</v>
+        <v>6.239307108901624</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08084344641128076</v>
+        <v>0.08093346417168379</v>
       </c>
       <c r="C33">
-        <v>293.39317118198</v>
+        <v>289.0116549289922</v>
       </c>
       <c r="D33">
-        <v>350.36217118198</v>
+        <v>349.9796549289922</v>
       </c>
       <c r="E33">
-        <v>113.369</v>
+        <v>117.368</v>
       </c>
       <c r="F33">
-        <v>123.969</v>
+        <v>127.968</v>
       </c>
       <c r="G33">
         <v>67</v>
@@ -3993,45 +3993,45 @@
         <v>42</v>
       </c>
       <c r="M33">
-        <v>6.7315167</v>
+        <v>7.076630400000001</v>
       </c>
       <c r="N33">
-        <v>35.2684833</v>
+        <v>34.9233696</v>
       </c>
       <c r="O33">
-        <v>8.817120825</v>
+        <v>8.7308424</v>
       </c>
       <c r="P33">
-        <v>26.451362475</v>
+        <v>26.1925272</v>
       </c>
       <c r="Q33">
-        <v>38.351362475</v>
+        <v>38.0925272</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09886767595837792</v>
+        <v>0.09950215319365266</v>
       </c>
       <c r="T33">
-        <v>1.034387779242104</v>
+        <v>1.046754921509466</v>
       </c>
       <c r="U33">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.239307108901624</v>
+        <v>5.935028060812671</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08093346417168379</v>
+        <v>0.08079098193208682</v>
       </c>
       <c r="C34">
-        <v>289.0116549289922</v>
+        <v>285.6184966240995</v>
       </c>
       <c r="D34">
-        <v>349.9796549289922</v>
+        <v>350.5854966240996</v>
       </c>
       <c r="E34">
-        <v>117.368</v>
+        <v>121.367</v>
       </c>
       <c r="F34">
-        <v>127.968</v>
+        <v>131.967</v>
       </c>
       <c r="G34">
         <v>67</v>
@@ -4075,28 +4075,28 @@
         <v>42</v>
       </c>
       <c r="M34">
-        <v>7.076630400000001</v>
+        <v>7.297775100000001</v>
       </c>
       <c r="N34">
-        <v>34.9233696</v>
+        <v>34.7022249</v>
       </c>
       <c r="O34">
-        <v>8.7308424</v>
+        <v>8.675556224999999</v>
       </c>
       <c r="P34">
-        <v>26.1925272</v>
+        <v>26.026668675</v>
       </c>
       <c r="Q34">
-        <v>38.0925272</v>
+        <v>37.92666867499999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09950215319365266</v>
+        <v>0.1001555700478908</v>
       </c>
       <c r="T34">
-        <v>1.046754921509466</v>
+        <v>1.059491232202718</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.935028060812671</v>
+        <v>5.755178725636529</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08079098193208682</v>
+        <v>0.08064849969248987</v>
       </c>
       <c r="C35">
-        <v>285.6184966240995</v>
+        <v>282.2274394735902</v>
       </c>
       <c r="D35">
-        <v>350.5854966240996</v>
+        <v>351.1934394735902</v>
       </c>
       <c r="E35">
-        <v>121.367</v>
+        <v>125.366</v>
       </c>
       <c r="F35">
-        <v>131.967</v>
+        <v>135.966</v>
       </c>
       <c r="G35">
         <v>67</v>
@@ -4157,28 +4157,28 @@
         <v>42</v>
       </c>
       <c r="M35">
-        <v>7.297775100000001</v>
+        <v>7.518919800000001</v>
       </c>
       <c r="N35">
-        <v>34.7022249</v>
+        <v>34.4810802</v>
       </c>
       <c r="O35">
-        <v>8.675556224999999</v>
+        <v>8.62027005</v>
       </c>
       <c r="P35">
-        <v>26.026668675</v>
+        <v>25.86081015</v>
       </c>
       <c r="Q35">
-        <v>37.92666867499999</v>
+        <v>37.76081015</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1001555700478908</v>
+        <v>0.1008287874128634</v>
       </c>
       <c r="T35">
-        <v>1.059491232202718</v>
+        <v>1.072613491704858</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.755178725636529</v>
+        <v>5.585908763117808</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08064849969248987</v>
+        <v>0.0805060174528929</v>
       </c>
       <c r="C36">
-        <v>282.2274394735902</v>
+        <v>278.8384944271529</v>
       </c>
       <c r="D36">
-        <v>351.1934394735902</v>
+        <v>351.8034944271529</v>
       </c>
       <c r="E36">
-        <v>125.366</v>
+        <v>129.365</v>
       </c>
       <c r="F36">
-        <v>135.966</v>
+        <v>139.965</v>
       </c>
       <c r="G36">
         <v>67</v>
@@ -4239,28 +4239,28 @@
         <v>42</v>
       </c>
       <c r="M36">
-        <v>7.518919800000001</v>
+        <v>7.740064500000002</v>
       </c>
       <c r="N36">
-        <v>34.4810802</v>
+        <v>34.2599355</v>
       </c>
       <c r="O36">
-        <v>8.62027005</v>
+        <v>8.564983874999999</v>
       </c>
       <c r="P36">
-        <v>25.86081015</v>
+        <v>25.694951625</v>
       </c>
       <c r="Q36">
-        <v>37.76081015</v>
+        <v>37.594951625</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1008287874128634</v>
+        <v>0.1015227191582968</v>
       </c>
       <c r="T36">
-        <v>1.072613491704858</v>
+        <v>1.086139513037832</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.585908763117808</v>
+        <v>5.42631136988587</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0805060174528929</v>
+        <v>0.08036353521329594</v>
       </c>
       <c r="C37">
-        <v>278.8384944271529</v>
+        <v>275.4516725106917</v>
       </c>
       <c r="D37">
-        <v>351.8034944271529</v>
+        <v>352.4156725106916</v>
       </c>
       <c r="E37">
-        <v>129.365</v>
+        <v>133.364</v>
       </c>
       <c r="F37">
-        <v>139.965</v>
+        <v>143.964</v>
       </c>
       <c r="G37">
         <v>67</v>
@@ -4321,28 +4321,28 @@
         <v>42</v>
       </c>
       <c r="M37">
-        <v>7.740064500000002</v>
+        <v>7.961209200000002</v>
       </c>
       <c r="N37">
-        <v>34.2599355</v>
+        <v>34.0387908</v>
       </c>
       <c r="O37">
-        <v>8.564983874999999</v>
+        <v>8.5096977</v>
       </c>
       <c r="P37">
-        <v>25.694951625</v>
+        <v>25.5290931</v>
       </c>
       <c r="Q37">
-        <v>37.594951625</v>
+        <v>37.4290931</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1015227191582968</v>
+        <v>0.1022383362707749</v>
       </c>
       <c r="T37">
-        <v>1.086139513037832</v>
+        <v>1.100088222537462</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.42631136988587</v>
+        <v>5.275580498500152</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08036353521329595</v>
+        <v>0.08022105297369897</v>
       </c>
       <c r="C38">
-        <v>275.4516725106915</v>
+        <v>272.0669848269891</v>
       </c>
       <c r="D38">
-        <v>352.4156725106915</v>
+        <v>353.0299848269891</v>
       </c>
       <c r="E38">
-        <v>133.364</v>
+        <v>137.363</v>
       </c>
       <c r="F38">
-        <v>143.964</v>
+        <v>147.963</v>
       </c>
       <c r="G38">
         <v>67</v>
@@ -4403,28 +4403,28 @@
         <v>42</v>
       </c>
       <c r="M38">
-        <v>7.9612092</v>
+        <v>8.182353900000001</v>
       </c>
       <c r="N38">
-        <v>34.0387908</v>
+        <v>33.8176461</v>
       </c>
       <c r="O38">
-        <v>8.5096977</v>
+        <v>8.454411524999999</v>
       </c>
       <c r="P38">
-        <v>25.5290931</v>
+        <v>25.363234575</v>
       </c>
       <c r="Q38">
-        <v>37.4290931</v>
+        <v>37.263234575</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1022383362707749</v>
+        <v>0.1029766713868238</v>
       </c>
       <c r="T38">
-        <v>1.100088222537462</v>
+        <v>1.114479748211683</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.275580498500153</v>
+        <v>5.132997241783931</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08022105297369897</v>
+        <v>0.080078570734102</v>
       </c>
       <c r="C39">
-        <v>272.0669848269891</v>
+        <v>268.6844425563785</v>
       </c>
       <c r="D39">
-        <v>353.0299848269891</v>
+        <v>353.6464425563785</v>
       </c>
       <c r="E39">
-        <v>137.363</v>
+        <v>141.362</v>
       </c>
       <c r="F39">
-        <v>147.963</v>
+        <v>151.962</v>
       </c>
       <c r="G39">
         <v>67</v>
@@ -4485,28 +4485,28 @@
         <v>42</v>
       </c>
       <c r="M39">
-        <v>8.182353900000001</v>
+        <v>8.403498600000001</v>
       </c>
       <c r="N39">
-        <v>33.8176461</v>
+        <v>33.5965014</v>
       </c>
       <c r="O39">
-        <v>8.454411524999999</v>
+        <v>8.39912535</v>
       </c>
       <c r="P39">
-        <v>25.363234575</v>
+        <v>25.19737605</v>
       </c>
       <c r="Q39">
-        <v>37.263234575</v>
+        <v>37.09737605</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1029766713868238</v>
+        <v>0.1037388237646807</v>
       </c>
       <c r="T39">
-        <v>1.114479748211683</v>
+        <v>1.129335516649588</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.132997241783931</v>
+        <v>4.997918367000144</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.080078570734102</v>
+        <v>0.07993608849450504</v>
       </c>
       <c r="C40">
-        <v>268.6844425563785</v>
+        <v>265.3040569574215</v>
       </c>
       <c r="D40">
-        <v>353.6464425563785</v>
+        <v>354.2650569574215</v>
       </c>
       <c r="E40">
-        <v>141.362</v>
+        <v>145.361</v>
       </c>
       <c r="F40">
-        <v>151.962</v>
+        <v>155.961</v>
       </c>
       <c r="G40">
         <v>67</v>
@@ -4567,28 +4567,28 @@
         <v>42</v>
       </c>
       <c r="M40">
-        <v>8.403498600000001</v>
+        <v>8.624643300000001</v>
       </c>
       <c r="N40">
-        <v>33.5965014</v>
+        <v>33.3753567</v>
       </c>
       <c r="O40">
-        <v>8.39912535</v>
+        <v>8.343839174999999</v>
       </c>
       <c r="P40">
-        <v>25.19737605</v>
+        <v>25.031517525</v>
       </c>
       <c r="Q40">
-        <v>37.09737605</v>
+        <v>36.931517525</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1037388237646807</v>
+        <v>0.1045259647450902</v>
       </c>
       <c r="T40">
-        <v>1.129335516649588</v>
+        <v>1.144678359462507</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.997918367000144</v>
+        <v>4.86976661400014</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07993608849450504</v>
+        <v>0.07979360625490806</v>
       </c>
       <c r="C41">
-        <v>265.3040569574215</v>
+        <v>261.9258393675938</v>
       </c>
       <c r="D41">
-        <v>354.2650569574215</v>
+        <v>354.8858393675939</v>
       </c>
       <c r="E41">
-        <v>145.361</v>
+        <v>149.36</v>
       </c>
       <c r="F41">
-        <v>155.961</v>
+        <v>159.96</v>
       </c>
       <c r="G41">
         <v>67</v>
@@ -4649,28 +4649,28 @@
         <v>42</v>
       </c>
       <c r="M41">
-        <v>8.624643300000001</v>
+        <v>8.845788000000002</v>
       </c>
       <c r="N41">
-        <v>33.3753567</v>
+        <v>33.154212</v>
       </c>
       <c r="O41">
-        <v>8.343839174999999</v>
+        <v>8.288553</v>
       </c>
       <c r="P41">
-        <v>25.031517525</v>
+        <v>24.865659</v>
       </c>
       <c r="Q41">
-        <v>36.931517525</v>
+        <v>36.765659</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1045259647450902</v>
+        <v>0.1053393437581801</v>
       </c>
       <c r="T41">
-        <v>1.144678359462507</v>
+        <v>1.16053263036919</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.86976661400014</v>
+        <v>4.748022448650136</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07979360625490806</v>
+        <v>0.0796511240153111</v>
       </c>
       <c r="C42">
-        <v>261.9258393675938</v>
+        <v>258.5498012039778</v>
       </c>
       <c r="D42">
-        <v>354.8858393675939</v>
+        <v>355.5088012039778</v>
       </c>
       <c r="E42">
-        <v>149.36</v>
+        <v>153.359</v>
       </c>
       <c r="F42">
-        <v>159.96</v>
+        <v>163.959</v>
       </c>
       <c r="G42">
         <v>67</v>
@@ -4731,28 +4731,28 @@
         <v>42</v>
       </c>
       <c r="M42">
-        <v>8.845788000000002</v>
+        <v>9.066932700000002</v>
       </c>
       <c r="N42">
-        <v>33.154212</v>
+        <v>32.9330673</v>
       </c>
       <c r="O42">
-        <v>8.288553</v>
+        <v>8.233266824999999</v>
       </c>
       <c r="P42">
-        <v>24.865659</v>
+        <v>24.699800475</v>
       </c>
       <c r="Q42">
-        <v>36.765659</v>
+        <v>36.599800475</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1053393437581801</v>
+        <v>0.1061802949412053</v>
       </c>
       <c r="T42">
-        <v>1.16053263036919</v>
+        <v>1.176924334187964</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.748022448650136</v>
+        <v>4.632217023073304</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0796511240153111</v>
+        <v>0.07950864177571414</v>
       </c>
       <c r="C43">
-        <v>258.5498012039778</v>
+        <v>255.1759539639623</v>
       </c>
       <c r="D43">
-        <v>355.5088012039778</v>
+        <v>356.1339539639624</v>
       </c>
       <c r="E43">
-        <v>153.359</v>
+        <v>157.358</v>
       </c>
       <c r="F43">
-        <v>163.959</v>
+        <v>167.958</v>
       </c>
       <c r="G43">
         <v>67</v>
@@ -4813,28 +4813,28 @@
         <v>42</v>
       </c>
       <c r="M43">
-        <v>9.066932700000002</v>
+        <v>9.288077400000002</v>
       </c>
       <c r="N43">
-        <v>32.9330673</v>
+        <v>32.71192259999999</v>
       </c>
       <c r="O43">
-        <v>8.233266824999999</v>
+        <v>8.177980649999999</v>
       </c>
       <c r="P43">
-        <v>24.699800475</v>
+        <v>24.53394195</v>
       </c>
       <c r="Q43">
-        <v>36.599800475</v>
+        <v>36.43394195</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1061802949412053</v>
+        <v>0.1070502444408864</v>
       </c>
       <c r="T43">
-        <v>1.176924334187964</v>
+        <v>1.193881269172902</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.632217023073304</v>
+        <v>4.521926141571558</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07950864177571415</v>
+        <v>0.08017240953611718</v>
       </c>
       <c r="C44">
-        <v>255.1759539639623</v>
+        <v>248.2832017419269</v>
       </c>
       <c r="D44">
-        <v>356.1339539639623</v>
+        <v>353.240201741927</v>
       </c>
       <c r="E44">
-        <v>157.358</v>
+        <v>161.357</v>
       </c>
       <c r="F44">
-        <v>167.958</v>
+        <v>171.957</v>
       </c>
       <c r="G44">
         <v>67</v>
@@ -4895,45 +4895,45 @@
         <v>42</v>
       </c>
       <c r="M44">
-        <v>9.288077400000001</v>
+        <v>9.939114600000002</v>
       </c>
       <c r="N44">
-        <v>32.7119226</v>
+        <v>32.0608854</v>
       </c>
       <c r="O44">
-        <v>8.17798065</v>
+        <v>8.015221349999999</v>
       </c>
       <c r="P44">
-        <v>24.53394195</v>
+        <v>24.04566405</v>
       </c>
       <c r="Q44">
-        <v>36.43394195</v>
+        <v>35.94566405</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1070502444408864</v>
+        <v>0.1079507184844161</v>
       </c>
       <c r="T44">
-        <v>1.193881269172902</v>
+        <v>1.211433184332751</v>
       </c>
       <c r="U44">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>4.521926141571559</v>
+        <v>4.225728517105537</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08017240953611718</v>
+        <v>0.08004867729652021</v>
       </c>
       <c r="C45">
-        <v>248.2832017419269</v>
+        <v>244.8200515878567</v>
       </c>
       <c r="D45">
-        <v>353.240201741927</v>
+        <v>353.7760515878567</v>
       </c>
       <c r="E45">
-        <v>161.357</v>
+        <v>165.356</v>
       </c>
       <c r="F45">
-        <v>171.957</v>
+        <v>175.956</v>
       </c>
       <c r="G45">
         <v>67</v>
@@ -4977,28 +4977,28 @@
         <v>42</v>
       </c>
       <c r="M45">
-        <v>9.939114600000002</v>
+        <v>10.1702568</v>
       </c>
       <c r="N45">
-        <v>32.0608854</v>
+        <v>31.8297432</v>
       </c>
       <c r="O45">
-        <v>8.015221349999999</v>
+        <v>7.957435799999999</v>
       </c>
       <c r="P45">
-        <v>24.04566405</v>
+        <v>23.8723074</v>
       </c>
       <c r="Q45">
-        <v>35.94566405</v>
+        <v>35.7723074</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1079507184844161</v>
+        <v>0.1088833523152146</v>
       </c>
       <c r="T45">
-        <v>1.211433184332751</v>
+        <v>1.229611953605452</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.225728517105537</v>
+        <v>4.129689232625865</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08004867729652021</v>
+        <v>0.07992494505692324</v>
       </c>
       <c r="C46">
-        <v>244.8200515878567</v>
+        <v>241.358529624966</v>
       </c>
       <c r="D46">
-        <v>353.7760515878567</v>
+        <v>354.313529624966</v>
       </c>
       <c r="E46">
-        <v>165.356</v>
+        <v>169.355</v>
       </c>
       <c r="F46">
-        <v>175.956</v>
+        <v>179.955</v>
       </c>
       <c r="G46">
         <v>67</v>
@@ -5059,28 +5059,28 @@
         <v>42</v>
       </c>
       <c r="M46">
-        <v>10.1702568</v>
+        <v>10.401399</v>
       </c>
       <c r="N46">
-        <v>31.8297432</v>
+        <v>31.598601</v>
       </c>
       <c r="O46">
-        <v>7.957435799999999</v>
+        <v>7.89965025</v>
       </c>
       <c r="P46">
-        <v>23.8723074</v>
+        <v>23.69895075</v>
       </c>
       <c r="Q46">
-        <v>35.7723074</v>
+        <v>35.59895075</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1088833523152146</v>
+        <v>0.1098499001034968</v>
       </c>
       <c r="T46">
-        <v>1.229611953605452</v>
+        <v>1.248451769033523</v>
       </c>
       <c r="U46">
         <v>0.0578</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.129689232625865</v>
+        <v>4.037918360789735</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07992494505692324</v>
+        <v>0.08100871281732627</v>
       </c>
       <c r="C47">
-        <v>241.358529624966</v>
+        <v>232.7065380400246</v>
       </c>
       <c r="D47">
-        <v>354.313529624966</v>
+        <v>349.6605380400246</v>
       </c>
       <c r="E47">
-        <v>169.355</v>
+        <v>173.354</v>
       </c>
       <c r="F47">
-        <v>179.955</v>
+        <v>183.954</v>
       </c>
       <c r="G47">
         <v>67</v>
@@ -5141,45 +5141,45 @@
         <v>42</v>
       </c>
       <c r="M47">
-        <v>10.401399</v>
+        <v>11.2763802</v>
       </c>
       <c r="N47">
-        <v>31.598601</v>
+        <v>30.7236198</v>
       </c>
       <c r="O47">
-        <v>7.89965025</v>
+        <v>7.68090495</v>
       </c>
       <c r="P47">
-        <v>23.69895075</v>
+        <v>23.04271485</v>
       </c>
       <c r="Q47">
-        <v>35.59895075</v>
+        <v>34.94271485</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1098499001034968</v>
+        <v>0.1108522459580116</v>
       </c>
       <c r="T47">
-        <v>1.248451769033523</v>
+        <v>1.267989355403374</v>
       </c>
       <c r="U47">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.037918360789735</v>
+        <v>3.7245994951465</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08100871281732627</v>
+        <v>0.08091123057772931</v>
       </c>
       <c r="C48">
-        <v>232.7065380400246</v>
+        <v>229.1210553814443</v>
       </c>
       <c r="D48">
-        <v>349.6605380400246</v>
+        <v>350.0740553814443</v>
       </c>
       <c r="E48">
-        <v>173.354</v>
+        <v>177.353</v>
       </c>
       <c r="F48">
-        <v>183.954</v>
+        <v>187.953</v>
       </c>
       <c r="G48">
         <v>67</v>
@@ -5223,28 +5223,28 @@
         <v>42</v>
       </c>
       <c r="M48">
-        <v>11.2763802</v>
+        <v>11.5215189</v>
       </c>
       <c r="N48">
-        <v>30.7236198</v>
+        <v>30.4784811</v>
       </c>
       <c r="O48">
-        <v>7.68090495</v>
+        <v>7.619620274999999</v>
       </c>
       <c r="P48">
-        <v>23.04271485</v>
+        <v>22.858860825</v>
       </c>
       <c r="Q48">
-        <v>34.94271485</v>
+        <v>34.758860825</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1108522459580116</v>
+        <v>0.1118924161843949</v>
       </c>
       <c r="T48">
-        <v>1.267989355403374</v>
+        <v>1.288264209183409</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.7245994951465</v>
+        <v>3.645352697377426</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08091123057772931</v>
+        <v>0.08081374833813235</v>
       </c>
       <c r="C49">
-        <v>229.1210553814443</v>
+        <v>225.5365519529305</v>
       </c>
       <c r="D49">
-        <v>350.0740553814443</v>
+        <v>350.4885519529305</v>
       </c>
       <c r="E49">
-        <v>177.353</v>
+        <v>181.352</v>
       </c>
       <c r="F49">
-        <v>187.953</v>
+        <v>191.952</v>
       </c>
       <c r="G49">
         <v>67</v>
@@ -5305,28 +5305,28 @@
         <v>42</v>
       </c>
       <c r="M49">
-        <v>11.5215189</v>
+        <v>11.7666576</v>
       </c>
       <c r="N49">
-        <v>30.4784811</v>
+        <v>30.2333424</v>
       </c>
       <c r="O49">
-        <v>7.619620274999999</v>
+        <v>7.558335599999999</v>
       </c>
       <c r="P49">
-        <v>22.858860825</v>
+        <v>22.6750068</v>
       </c>
       <c r="Q49">
-        <v>34.758860825</v>
+        <v>34.5750068</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1118924161843949</v>
+        <v>0.1129725929579468</v>
       </c>
       <c r="T49">
-        <v>1.288264209183409</v>
+        <v>1.309318865031907</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.645352697377426</v>
+        <v>3.569407849515396</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08081374833813233</v>
+        <v>0.08174526609853537</v>
       </c>
       <c r="C50">
-        <v>225.5365519529306</v>
+        <v>217.6163938032246</v>
       </c>
       <c r="D50">
-        <v>350.4885519529306</v>
+        <v>346.5673938032246</v>
       </c>
       <c r="E50">
-        <v>181.352</v>
+        <v>185.351</v>
       </c>
       <c r="F50">
-        <v>191.952</v>
+        <v>195.951</v>
       </c>
       <c r="G50">
         <v>67</v>
@@ -5387,45 +5387,45 @@
         <v>42</v>
       </c>
       <c r="M50">
-        <v>11.7666576</v>
+        <v>12.5604591</v>
       </c>
       <c r="N50">
-        <v>30.2333424</v>
+        <v>29.4395409</v>
       </c>
       <c r="O50">
-        <v>7.558335599999999</v>
+        <v>7.359885224999999</v>
       </c>
       <c r="P50">
-        <v>22.6750068</v>
+        <v>22.079655675</v>
       </c>
       <c r="Q50">
-        <v>34.5750068</v>
+        <v>33.979655675</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1129725929579468</v>
+        <v>0.1140951296049713</v>
       </c>
       <c r="T50">
-        <v>1.309318865031907</v>
+        <v>1.331199193658777</v>
       </c>
       <c r="U50">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.569407849515397</v>
+        <v>3.343826819196441</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08174526609853537</v>
+        <v>0.0816687838589384</v>
       </c>
       <c r="C51">
-        <v>217.6163938032246</v>
+        <v>213.9360312330574</v>
       </c>
       <c r="D51">
-        <v>346.5673938032246</v>
+        <v>346.8860312330574</v>
       </c>
       <c r="E51">
-        <v>185.351</v>
+        <v>189.35</v>
       </c>
       <c r="F51">
-        <v>195.951</v>
+        <v>199.95</v>
       </c>
       <c r="G51">
         <v>67</v>
@@ -5469,28 +5469,28 @@
         <v>42</v>
       </c>
       <c r="M51">
-        <v>12.5604591</v>
+        <v>12.816795</v>
       </c>
       <c r="N51">
-        <v>29.4395409</v>
+        <v>29.183205</v>
       </c>
       <c r="O51">
-        <v>7.359885224999999</v>
+        <v>7.295801249999999</v>
       </c>
       <c r="P51">
-        <v>22.079655675</v>
+        <v>21.88740375</v>
       </c>
       <c r="Q51">
-        <v>33.979655675</v>
+        <v>33.78740375</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1140951296049713</v>
+        <v>0.1152625677178768</v>
       </c>
       <c r="T51">
-        <v>1.331199193658777</v>
+        <v>1.353954735430722</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.343826819196441</v>
+        <v>3.276950282812512</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0816687838589384</v>
+        <v>0.08159230161934145</v>
       </c>
       <c r="C52">
-        <v>213.9360312330574</v>
+        <v>210.2562551187823</v>
       </c>
       <c r="D52">
-        <v>346.8860312330574</v>
+        <v>347.2052551187824</v>
       </c>
       <c r="E52">
-        <v>189.35</v>
+        <v>193.349</v>
       </c>
       <c r="F52">
-        <v>199.95</v>
+        <v>203.949</v>
       </c>
       <c r="G52">
         <v>67</v>
@@ -5551,28 +5551,28 @@
         <v>42</v>
       </c>
       <c r="M52">
-        <v>12.816795</v>
+        <v>13.0731309</v>
       </c>
       <c r="N52">
-        <v>29.183205</v>
+        <v>28.9268691</v>
       </c>
       <c r="O52">
-        <v>7.295801249999999</v>
+        <v>7.231717274999999</v>
       </c>
       <c r="P52">
-        <v>21.88740375</v>
+        <v>21.695151825</v>
       </c>
       <c r="Q52">
-        <v>33.78740375</v>
+        <v>33.59515182499999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1152625677178768</v>
+        <v>0.1164776563660029</v>
       </c>
       <c r="T52">
-        <v>1.353954735430722</v>
+        <v>1.377639074826011</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.276950282812512</v>
+        <v>3.212696355698542</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08159230161934145</v>
+        <v>0.08151581937974446</v>
       </c>
       <c r="C53">
-        <v>210.2562551187823</v>
+        <v>206.5770670809595</v>
       </c>
       <c r="D53">
-        <v>347.2052551187824</v>
+        <v>347.5250670809595</v>
       </c>
       <c r="E53">
-        <v>193.349</v>
+        <v>197.348</v>
       </c>
       <c r="F53">
-        <v>203.949</v>
+        <v>207.948</v>
       </c>
       <c r="G53">
         <v>67</v>
@@ -5633,28 +5633,28 @@
         <v>42</v>
       </c>
       <c r="M53">
-        <v>13.0731309</v>
+        <v>13.3294668</v>
       </c>
       <c r="N53">
-        <v>28.9268691</v>
+        <v>28.67053319999999</v>
       </c>
       <c r="O53">
-        <v>7.231717274999999</v>
+        <v>7.167633299999999</v>
       </c>
       <c r="P53">
-        <v>21.695151825</v>
+        <v>21.5028999</v>
       </c>
       <c r="Q53">
-        <v>33.59515182499999</v>
+        <v>33.40289989999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1164776563660029</v>
+        <v>0.117743373707801</v>
       </c>
       <c r="T53">
-        <v>1.377639074826011</v>
+        <v>1.402310261696105</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.212696355698542</v>
+        <v>3.150913733473569</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08151581937974446</v>
+        <v>0.08143933714014751</v>
       </c>
       <c r="C54">
-        <v>206.5770670809595</v>
+        <v>202.8984687461243</v>
       </c>
       <c r="D54">
-        <v>347.5250670809595</v>
+        <v>347.8454687461244</v>
       </c>
       <c r="E54">
-        <v>197.348</v>
+        <v>201.347</v>
       </c>
       <c r="F54">
-        <v>207.948</v>
+        <v>211.947</v>
       </c>
       <c r="G54">
         <v>67</v>
@@ -5715,28 +5715,28 @@
         <v>42</v>
       </c>
       <c r="M54">
-        <v>13.3294668</v>
+        <v>13.5858027</v>
       </c>
       <c r="N54">
-        <v>28.67053319999999</v>
+        <v>28.4141973</v>
       </c>
       <c r="O54">
-        <v>7.167633299999999</v>
+        <v>7.103549324999999</v>
       </c>
       <c r="P54">
-        <v>21.5028999</v>
+        <v>21.310647975</v>
       </c>
       <c r="Q54">
-        <v>33.40289989999999</v>
+        <v>33.210647975</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.117743373707801</v>
+        <v>0.119062951362016</v>
       </c>
       <c r="T54">
-        <v>1.402310261696105</v>
+        <v>1.428031286305351</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.150913733473569</v>
+        <v>3.0914625309552</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08143933714014751</v>
+        <v>0.08136285490055054</v>
       </c>
       <c r="C55">
-        <v>202.8984687461243</v>
+        <v>199.2204617468171</v>
       </c>
       <c r="D55">
-        <v>347.8454687461244</v>
+        <v>348.1664617468172</v>
       </c>
       <c r="E55">
-        <v>201.347</v>
+        <v>205.346</v>
       </c>
       <c r="F55">
-        <v>211.947</v>
+        <v>215.946</v>
       </c>
       <c r="G55">
         <v>67</v>
@@ -5797,28 +5797,28 @@
         <v>42</v>
       </c>
       <c r="M55">
-        <v>13.5858027</v>
+        <v>13.8421386</v>
       </c>
       <c r="N55">
-        <v>28.4141973</v>
+        <v>28.1578614</v>
       </c>
       <c r="O55">
-        <v>7.103549324999999</v>
+        <v>7.03946535</v>
       </c>
       <c r="P55">
-        <v>21.310647975</v>
+        <v>21.11839605</v>
       </c>
       <c r="Q55">
-        <v>33.210647975</v>
+        <v>33.01839605</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.119062951362016</v>
+        <v>0.1204399019577186</v>
       </c>
       <c r="T55">
-        <v>1.428031286305351</v>
+        <v>1.454870616332391</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.0914625309552</v>
+        <v>3.0342132248264</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08136285490055054</v>
+        <v>0.08450387266095356</v>
       </c>
       <c r="C56">
-        <v>199.2204617468171</v>
+        <v>182.5083704042815</v>
       </c>
       <c r="D56">
-        <v>348.1664617468172</v>
+        <v>335.4533704042816</v>
       </c>
       <c r="E56">
-        <v>205.346</v>
+        <v>209.3450000000001</v>
       </c>
       <c r="F56">
-        <v>215.946</v>
+        <v>219.9450000000001</v>
       </c>
       <c r="G56">
         <v>67</v>
@@ -5879,45 +5879,45 @@
         <v>42</v>
       </c>
       <c r="M56">
-        <v>13.8421386</v>
+        <v>15.8140455</v>
       </c>
       <c r="N56">
-        <v>28.1578614</v>
+        <v>26.18595449999999</v>
       </c>
       <c r="O56">
-        <v>7.03946535</v>
+        <v>6.546488624999999</v>
       </c>
       <c r="P56">
-        <v>21.11839605</v>
+        <v>19.639465875</v>
       </c>
       <c r="Q56">
-        <v>33.01839605</v>
+        <v>31.539465875</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1204399019577186</v>
+        <v>0.1218780503576746</v>
       </c>
       <c r="T56">
-        <v>1.454870616332391</v>
+        <v>1.482902805471743</v>
       </c>
       <c r="U56">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.0342132248264</v>
+        <v>2.655866900092072</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08450387266095356</v>
+        <v>0.0844858904213566</v>
       </c>
       <c r="C57">
-        <v>182.5083704042815</v>
+        <v>178.5795095669864</v>
       </c>
       <c r="D57">
-        <v>335.4533704042816</v>
+        <v>335.5235095669864</v>
       </c>
       <c r="E57">
-        <v>209.3450000000001</v>
+        <v>213.3440000000001</v>
       </c>
       <c r="F57">
-        <v>219.9450000000001</v>
+        <v>223.944</v>
       </c>
       <c r="G57">
         <v>67</v>
@@ -5961,28 +5961,28 @@
         <v>42</v>
       </c>
       <c r="M57">
-        <v>15.8140455</v>
+        <v>16.10157360000001</v>
       </c>
       <c r="N57">
-        <v>26.18595449999999</v>
+        <v>25.89842639999999</v>
       </c>
       <c r="O57">
-        <v>6.546488624999999</v>
+        <v>6.474606599999999</v>
       </c>
       <c r="P57">
-        <v>19.639465875</v>
+        <v>19.4238198</v>
       </c>
       <c r="Q57">
-        <v>31.539465875</v>
+        <v>31.3238198</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1218780503576746</v>
+        <v>0.1233815691394468</v>
       </c>
       <c r="T57">
-        <v>1.482902805471743</v>
+        <v>1.51220918502652</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.655866900092072</v>
+        <v>2.608440705447571</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0844858904213566</v>
+        <v>0.08446790818175963</v>
       </c>
       <c r="C58">
-        <v>178.5795095669864</v>
+        <v>174.650678066293</v>
       </c>
       <c r="D58">
-        <v>335.5235095669864</v>
+        <v>335.5936780662931</v>
       </c>
       <c r="E58">
-        <v>213.3440000000001</v>
+        <v>217.343</v>
       </c>
       <c r="F58">
-        <v>223.944</v>
+        <v>227.943</v>
       </c>
       <c r="G58">
         <v>67</v>
@@ -6043,28 +6043,28 @@
         <v>42</v>
       </c>
       <c r="M58">
-        <v>16.10157360000001</v>
+        <v>16.3891017</v>
       </c>
       <c r="N58">
-        <v>25.89842639999999</v>
+        <v>25.6108983</v>
       </c>
       <c r="O58">
-        <v>6.474606599999999</v>
+        <v>6.402724574999999</v>
       </c>
       <c r="P58">
-        <v>19.4238198</v>
+        <v>19.20817372499999</v>
       </c>
       <c r="Q58">
-        <v>31.3238198</v>
+        <v>31.10817372499999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1233815691394468</v>
+        <v>0.124955019027348</v>
       </c>
       <c r="T58">
-        <v>1.51220918502652</v>
+        <v>1.54287865200245</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.608440705447571</v>
+        <v>2.56267858780814</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08446790818175963</v>
+        <v>0.08444992594216266</v>
       </c>
       <c r="C59">
-        <v>174.650678066293</v>
+        <v>170.7218759206108</v>
       </c>
       <c r="D59">
-        <v>335.5936780662931</v>
+        <v>335.6638759206108</v>
       </c>
       <c r="E59">
-        <v>217.343</v>
+        <v>221.342</v>
       </c>
       <c r="F59">
-        <v>227.943</v>
+        <v>231.942</v>
       </c>
       <c r="G59">
         <v>67</v>
@@ -6125,28 +6125,28 @@
         <v>42</v>
       </c>
       <c r="M59">
-        <v>16.3891017</v>
+        <v>16.6766298</v>
       </c>
       <c r="N59">
-        <v>25.6108983</v>
+        <v>25.3233702</v>
       </c>
       <c r="O59">
-        <v>6.402724574999999</v>
+        <v>6.330842549999999</v>
       </c>
       <c r="P59">
-        <v>19.20817372499999</v>
+        <v>18.99252765</v>
       </c>
       <c r="Q59">
-        <v>31.10817372499999</v>
+        <v>30.89252765</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.124955019027348</v>
+        <v>0.1266033951003873</v>
       </c>
       <c r="T59">
-        <v>1.54287865200245</v>
+        <v>1.575008569786758</v>
       </c>
       <c r="U59">
         <v>0.07190000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.56267858780814</v>
+        <v>2.518494474225241</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08444992594216268</v>
+        <v>0.08615769370256571</v>
       </c>
       <c r="C60">
-        <v>170.7218759206107</v>
+        <v>160.1846957007639</v>
       </c>
       <c r="D60">
-        <v>335.6638759206107</v>
+        <v>329.1256957007639</v>
       </c>
       <c r="E60">
-        <v>221.342</v>
+        <v>225.341</v>
       </c>
       <c r="F60">
-        <v>231.942</v>
+        <v>235.941</v>
       </c>
       <c r="G60">
         <v>67</v>
@@ -6207,45 +6207,45 @@
         <v>42</v>
       </c>
       <c r="M60">
-        <v>16.6766298</v>
+        <v>17.8843278</v>
       </c>
       <c r="N60">
-        <v>25.3233702</v>
+        <v>24.1156722</v>
       </c>
       <c r="O60">
-        <v>6.33084255</v>
+        <v>6.02891805</v>
       </c>
       <c r="P60">
-        <v>18.99252765</v>
+        <v>18.08675415</v>
       </c>
       <c r="Q60">
-        <v>30.89252765</v>
+        <v>29.98675415</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1266033951003873</v>
+        <v>0.1283321797623554</v>
       </c>
       <c r="T60">
-        <v>1.575008569786758</v>
+        <v>1.608705800633714</v>
       </c>
       <c r="U60">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V60">
         <v>0.25</v>
       </c>
       <c r="W60">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.518494474225242</v>
+        <v>2.348424859445934</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08615769370256571</v>
+        <v>0.08616896146296874</v>
       </c>
       <c r="C61">
-        <v>160.1846957007639</v>
+        <v>156.1434028407638</v>
       </c>
       <c r="D61">
-        <v>329.1256957007639</v>
+        <v>329.0834028407638</v>
       </c>
       <c r="E61">
-        <v>225.341</v>
+        <v>229.34</v>
       </c>
       <c r="F61">
-        <v>235.941</v>
+        <v>239.94</v>
       </c>
       <c r="G61">
         <v>67</v>
@@ -6289,28 +6289,28 @@
         <v>42</v>
       </c>
       <c r="M61">
-        <v>17.8843278</v>
+        <v>18.187452</v>
       </c>
       <c r="N61">
-        <v>24.1156722</v>
+        <v>23.812548</v>
       </c>
       <c r="O61">
-        <v>6.02891805</v>
+        <v>5.953137</v>
       </c>
       <c r="P61">
-        <v>18.08675415</v>
+        <v>17.859411</v>
       </c>
       <c r="Q61">
-        <v>29.98675415</v>
+        <v>29.759411</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1283321797623554</v>
+        <v>0.1301474036574218</v>
       </c>
       <c r="T61">
-        <v>1.608705800633714</v>
+        <v>1.644087893023019</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.348424859445934</v>
+        <v>2.309284445121834</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08616896146296874</v>
+        <v>0.08618022922337176</v>
       </c>
       <c r="C62">
-        <v>156.1434028407638</v>
+        <v>152.1021208486856</v>
       </c>
       <c r="D62">
-        <v>329.0834028407638</v>
+        <v>329.0411208486856</v>
       </c>
       <c r="E62">
-        <v>229.34</v>
+        <v>233.339</v>
       </c>
       <c r="F62">
-        <v>239.94</v>
+        <v>243.939</v>
       </c>
       <c r="G62">
         <v>67</v>
@@ -6371,28 +6371,28 @@
         <v>42</v>
       </c>
       <c r="M62">
-        <v>18.187452</v>
+        <v>18.4905762</v>
       </c>
       <c r="N62">
-        <v>23.812548</v>
+        <v>23.5094238</v>
       </c>
       <c r="O62">
-        <v>5.953137</v>
+        <v>5.877355949999999</v>
       </c>
       <c r="P62">
-        <v>17.859411</v>
+        <v>17.63206785</v>
       </c>
       <c r="Q62">
-        <v>29.759411</v>
+        <v>29.53206785</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1301474036574218</v>
+        <v>0.1320557159573635</v>
       </c>
       <c r="T62">
-        <v>1.644087893023019</v>
+        <v>1.681284451688699</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.309284445121834</v>
+        <v>2.271427323070657</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08618022922337176</v>
+        <v>0.0861914969837748</v>
       </c>
       <c r="C63">
-        <v>152.1021208486856</v>
+        <v>148.0608497203408</v>
       </c>
       <c r="D63">
-        <v>329.0411208486856</v>
+        <v>328.9988497203408</v>
       </c>
       <c r="E63">
-        <v>233.339</v>
+        <v>237.338</v>
       </c>
       <c r="F63">
-        <v>243.939</v>
+        <v>247.938</v>
       </c>
       <c r="G63">
         <v>67</v>
@@ -6453,28 +6453,28 @@
         <v>42</v>
       </c>
       <c r="M63">
-        <v>18.4905762</v>
+        <v>18.7937004</v>
       </c>
       <c r="N63">
-        <v>23.5094238</v>
+        <v>23.2062996</v>
       </c>
       <c r="O63">
-        <v>5.877355949999999</v>
+        <v>5.801574899999999</v>
       </c>
       <c r="P63">
-        <v>17.63206785</v>
+        <v>17.4047247</v>
       </c>
       <c r="Q63">
-        <v>29.53206785</v>
+        <v>29.3047247</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1320557159573635</v>
+        <v>0.1340644657467758</v>
       </c>
       <c r="T63">
-        <v>1.681284451688699</v>
+        <v>1.720438723968361</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.271427323070657</v>
+        <v>2.234791398505001</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.0861914969837748</v>
+        <v>0.08620276474417785</v>
       </c>
       <c r="C64">
-        <v>148.0608497203408</v>
+        <v>144.0195894515431</v>
       </c>
       <c r="D64">
-        <v>328.9988497203408</v>
+        <v>328.9565894515431</v>
       </c>
       <c r="E64">
-        <v>237.338</v>
+        <v>241.337</v>
       </c>
       <c r="F64">
-        <v>247.938</v>
+        <v>251.937</v>
       </c>
       <c r="G64">
         <v>67</v>
@@ -6535,28 +6535,28 @@
         <v>42</v>
       </c>
       <c r="M64">
-        <v>18.7937004</v>
+        <v>19.0968246</v>
       </c>
       <c r="N64">
-        <v>23.2062996</v>
+        <v>22.9031754</v>
       </c>
       <c r="O64">
-        <v>5.801574899999999</v>
+        <v>5.72579385</v>
       </c>
       <c r="P64">
-        <v>17.4047247</v>
+        <v>17.17738155</v>
       </c>
       <c r="Q64">
-        <v>29.3047247</v>
+        <v>29.07738155</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1340644657467758</v>
+        <v>0.1361817966058861</v>
       </c>
       <c r="T64">
-        <v>1.720438723968361</v>
+        <v>1.761709443398275</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.234791398505001</v>
+        <v>2.199318519163652</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08620276474417785</v>
+        <v>0.08621403250458087</v>
       </c>
       <c r="C65">
-        <v>144.0195894515431</v>
+        <v>139.9783400381082</v>
       </c>
       <c r="D65">
-        <v>328.9565894515431</v>
+        <v>328.9143400381083</v>
       </c>
       <c r="E65">
-        <v>241.337</v>
+        <v>245.336</v>
       </c>
       <c r="F65">
-        <v>251.937</v>
+        <v>255.936</v>
       </c>
       <c r="G65">
         <v>67</v>
@@ -6617,28 +6617,28 @@
         <v>42</v>
       </c>
       <c r="M65">
-        <v>19.0968246</v>
+        <v>19.3999488</v>
       </c>
       <c r="N65">
-        <v>22.9031754</v>
+        <v>22.6000512</v>
       </c>
       <c r="O65">
-        <v>5.72579385</v>
+        <v>5.650012799999999</v>
       </c>
       <c r="P65">
-        <v>17.17738155</v>
+        <v>16.9500384</v>
       </c>
       <c r="Q65">
-        <v>29.07738155</v>
+        <v>28.8500384</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1361817966058861</v>
+        <v>0.1384167569571691</v>
       </c>
       <c r="T65">
-        <v>1.761709443398275</v>
+        <v>1.805272980574296</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.199318519163652</v>
+        <v>2.164954167301719</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08621403250458087</v>
+        <v>0.0862253002649839</v>
       </c>
       <c r="C66">
-        <v>139.9783400381082</v>
+        <v>135.9371014758541</v>
       </c>
       <c r="D66">
-        <v>328.9143400381083</v>
+        <v>328.8721014758542</v>
       </c>
       <c r="E66">
-        <v>245.336</v>
+        <v>249.3350000000001</v>
       </c>
       <c r="F66">
-        <v>255.936</v>
+        <v>259.9350000000001</v>
       </c>
       <c r="G66">
         <v>67</v>
@@ -6699,28 +6699,28 @@
         <v>42</v>
       </c>
       <c r="M66">
-        <v>19.3999488</v>
+        <v>19.70307300000001</v>
       </c>
       <c r="N66">
-        <v>22.6000512</v>
+        <v>22.29692699999999</v>
       </c>
       <c r="O66">
-        <v>5.650012799999999</v>
+        <v>5.574231749999998</v>
       </c>
       <c r="P66">
-        <v>16.9500384</v>
+        <v>16.72269524999999</v>
       </c>
       <c r="Q66">
-        <v>28.8500384</v>
+        <v>28.62269524999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1384167569571691</v>
+        <v>0.1407794293285254</v>
       </c>
       <c r="T66">
-        <v>1.805272980574296</v>
+        <v>1.851325862731803</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.164954167301719</v>
+        <v>2.131647180112462</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0862253002649839</v>
+        <v>0.08623656802538693</v>
       </c>
       <c r="C67">
-        <v>135.9371014758541</v>
+        <v>131.895873760601</v>
       </c>
       <c r="D67">
-        <v>328.8721014758542</v>
+        <v>328.829873760601</v>
       </c>
       <c r="E67">
-        <v>249.3350000000001</v>
+        <v>253.334</v>
       </c>
       <c r="F67">
-        <v>259.9350000000001</v>
+        <v>263.934</v>
       </c>
       <c r="G67">
         <v>67</v>
@@ -6781,28 +6781,28 @@
         <v>42</v>
       </c>
       <c r="M67">
-        <v>19.70307300000001</v>
+        <v>20.0061972</v>
       </c>
       <c r="N67">
-        <v>22.29692699999999</v>
+        <v>21.9938028</v>
       </c>
       <c r="O67">
-        <v>5.574231749999998</v>
+        <v>5.498450699999999</v>
       </c>
       <c r="P67">
-        <v>16.72269524999999</v>
+        <v>16.4953521</v>
       </c>
       <c r="Q67">
-        <v>28.62269524999999</v>
+        <v>28.3953521</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1407794293285254</v>
+        <v>0.1432810824276086</v>
       </c>
       <c r="T67">
-        <v>1.851325862731803</v>
+        <v>1.900087737957399</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.131647180112462</v>
+        <v>2.099349495565304</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08623656802538693</v>
+        <v>0.08624783578578997</v>
       </c>
       <c r="C68">
-        <v>131.895873760601</v>
+        <v>127.8546568881707</v>
       </c>
       <c r="D68">
-        <v>328.829873760601</v>
+        <v>328.7876568881707</v>
       </c>
       <c r="E68">
-        <v>253.334</v>
+        <v>257.333</v>
       </c>
       <c r="F68">
-        <v>263.934</v>
+        <v>267.933</v>
       </c>
       <c r="G68">
         <v>67</v>
@@ -6863,28 +6863,28 @@
         <v>42</v>
       </c>
       <c r="M68">
-        <v>20.0061972</v>
+        <v>20.30932140000001</v>
       </c>
       <c r="N68">
-        <v>21.9938028</v>
+        <v>21.69067859999999</v>
       </c>
       <c r="O68">
-        <v>5.498450699999999</v>
+        <v>5.422669649999999</v>
       </c>
       <c r="P68">
-        <v>16.4953521</v>
+        <v>16.26800895</v>
       </c>
       <c r="Q68">
-        <v>28.3953521</v>
+        <v>28.16800894999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1432810824276086</v>
+        <v>0.1459343508660302</v>
       </c>
       <c r="T68">
-        <v>1.900087737957399</v>
+        <v>1.951804878348183</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.099349495565304</v>
+        <v>2.068015921004627</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08624783578578997</v>
+        <v>0.086259103546193</v>
       </c>
       <c r="C69">
-        <v>127.8546568881707</v>
+        <v>123.813450854388</v>
       </c>
       <c r="D69">
-        <v>328.7876568881707</v>
+        <v>328.745450854388</v>
       </c>
       <c r="E69">
-        <v>257.333</v>
+        <v>261.332</v>
       </c>
       <c r="F69">
-        <v>267.933</v>
+        <v>271.932</v>
       </c>
       <c r="G69">
         <v>67</v>
@@ -6945,28 +6945,28 @@
         <v>42</v>
       </c>
       <c r="M69">
-        <v>20.30932140000001</v>
+        <v>20.6124456</v>
       </c>
       <c r="N69">
-        <v>21.69067859999999</v>
+        <v>21.3875544</v>
       </c>
       <c r="O69">
-        <v>5.422669649999999</v>
+        <v>5.346888599999999</v>
       </c>
       <c r="P69">
-        <v>16.26800895</v>
+        <v>16.0406658</v>
       </c>
       <c r="Q69">
-        <v>28.16800894999999</v>
+        <v>27.9406658</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1459343508660302</v>
+        <v>0.1487534485818531</v>
       </c>
       <c r="T69">
-        <v>1.951804878348183</v>
+        <v>2.006754340013392</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.068015921004627</v>
+        <v>2.037603922166324</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.086259103546193</v>
+        <v>0.08627037130659602</v>
       </c>
       <c r="C70">
-        <v>123.813450854388</v>
+        <v>119.7722556550791</v>
       </c>
       <c r="D70">
-        <v>328.745450854388</v>
+        <v>328.7032556550791</v>
       </c>
       <c r="E70">
-        <v>261.332</v>
+        <v>265.331</v>
       </c>
       <c r="F70">
-        <v>271.932</v>
+        <v>275.931</v>
       </c>
       <c r="G70">
         <v>67</v>
@@ -7027,28 +7027,28 @@
         <v>42</v>
       </c>
       <c r="M70">
-        <v>20.6124456</v>
+        <v>20.9155698</v>
       </c>
       <c r="N70">
-        <v>21.3875544</v>
+        <v>21.0844302</v>
       </c>
       <c r="O70">
-        <v>5.346888599999999</v>
+        <v>5.271107549999999</v>
       </c>
       <c r="P70">
-        <v>16.0406658</v>
+        <v>15.81332265</v>
       </c>
       <c r="Q70">
-        <v>27.9406658</v>
+        <v>27.71332264999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1487534485818531</v>
+        <v>0.1517544235696646</v>
       </c>
       <c r="T70">
-        <v>2.006754340013392</v>
+        <v>2.065248928237645</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.037603922166324</v>
+        <v>2.008073430540725</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08627037130659602</v>
+        <v>0.09373663906699907</v>
       </c>
       <c r="C71">
-        <v>119.7722556550791</v>
+        <v>90.00862626693606</v>
       </c>
       <c r="D71">
-        <v>328.7032556550791</v>
+        <v>302.9386262669361</v>
       </c>
       <c r="E71">
-        <v>265.331</v>
+        <v>269.33</v>
       </c>
       <c r="F71">
-        <v>275.931</v>
+        <v>279.9300000000001</v>
       </c>
       <c r="G71">
         <v>67</v>
@@ -7109,45 +7109,45 @@
         <v>42</v>
       </c>
       <c r="M71">
-        <v>20.9155698</v>
+        <v>25.1937</v>
       </c>
       <c r="N71">
-        <v>21.0844302</v>
+        <v>16.8063</v>
       </c>
       <c r="O71">
-        <v>5.271107549999999</v>
+        <v>4.201574999999999</v>
       </c>
       <c r="P71">
-        <v>15.81332265</v>
+        <v>12.604725</v>
       </c>
       <c r="Q71">
-        <v>27.71332264999999</v>
+        <v>24.504725</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1517544235696646</v>
+        <v>0.1549554635566636</v>
       </c>
       <c r="T71">
-        <v>2.065248928237645</v>
+        <v>2.127643155676849</v>
       </c>
       <c r="U71">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V71">
         <v>0.25</v>
       </c>
       <c r="W71">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y71">
-        <v>2.008073430540725</v>
+        <v>1.667083437526048</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09373663906699907</v>
+        <v>0.09385440682740211</v>
       </c>
       <c r="C72">
-        <v>90.00862626693606</v>
+        <v>85.63554945247705</v>
       </c>
       <c r="D72">
-        <v>302.9386262669361</v>
+        <v>302.5645494524771</v>
       </c>
       <c r="E72">
-        <v>269.33</v>
+        <v>273.329</v>
       </c>
       <c r="F72">
-        <v>279.9300000000001</v>
+        <v>283.929</v>
       </c>
       <c r="G72">
         <v>67</v>
@@ -7191,28 +7191,28 @@
         <v>42</v>
       </c>
       <c r="M72">
-        <v>25.1937</v>
+        <v>25.55361</v>
       </c>
       <c r="N72">
-        <v>16.8063</v>
+        <v>16.44639</v>
       </c>
       <c r="O72">
-        <v>4.201574999999999</v>
+        <v>4.111597499999999</v>
       </c>
       <c r="P72">
-        <v>12.604725</v>
+        <v>12.3347925</v>
       </c>
       <c r="Q72">
-        <v>24.504725</v>
+        <v>24.2347925</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1549554635566636</v>
+        <v>0.1583772649220762</v>
       </c>
       <c r="T72">
-        <v>2.127643155676849</v>
+        <v>2.194340433284274</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.667083437526048</v>
+        <v>1.643603389110188</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09385440682740211</v>
+        <v>0.09397217458780514</v>
       </c>
       <c r="C73">
-        <v>85.63554945247705</v>
+        <v>81.26339533899096</v>
       </c>
       <c r="D73">
-        <v>302.5645494524771</v>
+        <v>302.191395338991</v>
       </c>
       <c r="E73">
-        <v>273.329</v>
+        <v>277.328</v>
       </c>
       <c r="F73">
-        <v>283.929</v>
+        <v>287.928</v>
       </c>
       <c r="G73">
         <v>67</v>
@@ -7273,28 +7273,28 @@
         <v>42</v>
       </c>
       <c r="M73">
-        <v>25.55361</v>
+        <v>25.91352</v>
       </c>
       <c r="N73">
-        <v>16.44639</v>
+        <v>16.08648</v>
       </c>
       <c r="O73">
-        <v>4.111597499999999</v>
+        <v>4.02162</v>
       </c>
       <c r="P73">
-        <v>12.3347925</v>
+        <v>12.06486</v>
       </c>
       <c r="Q73">
-        <v>24.2347925</v>
+        <v>23.96486</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1583772649220762</v>
+        <v>0.1620434806707326</v>
       </c>
       <c r="T73">
-        <v>2.194340433284273</v>
+        <v>2.265801802149371</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.643603389110188</v>
+        <v>1.620775564261436</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09397217458780514</v>
+        <v>0.09408994234820817</v>
       </c>
       <c r="C74">
-        <v>81.26339533899096</v>
+        <v>76.89216051677016</v>
       </c>
       <c r="D74">
-        <v>302.191395338991</v>
+        <v>301.8191605167702</v>
       </c>
       <c r="E74">
-        <v>277.328</v>
+        <v>281.327</v>
       </c>
       <c r="F74">
-        <v>287.928</v>
+        <v>291.927</v>
       </c>
       <c r="G74">
         <v>67</v>
@@ -7355,28 +7355,28 @@
         <v>42</v>
       </c>
       <c r="M74">
-        <v>25.91352</v>
+        <v>26.27343</v>
       </c>
       <c r="N74">
-        <v>16.08648</v>
+        <v>15.72657</v>
       </c>
       <c r="O74">
-        <v>4.02162</v>
+        <v>3.9316425</v>
       </c>
       <c r="P74">
-        <v>12.06486</v>
+        <v>11.7949275</v>
       </c>
       <c r="Q74">
-        <v>23.96486</v>
+        <v>23.6949275</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1620434806707326</v>
+        <v>0.1659812679563265</v>
       </c>
       <c r="T74">
-        <v>2.265801802149371</v>
+        <v>2.342556605745217</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.620775564261436</v>
+        <v>1.598573159271553</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09408994234820817</v>
+        <v>0.0942077101086112</v>
       </c>
       <c r="C75">
-        <v>76.89216051677016</v>
+        <v>72.52184159288652</v>
       </c>
       <c r="D75">
-        <v>301.8191605167702</v>
+        <v>301.4478415928866</v>
       </c>
       <c r="E75">
-        <v>281.327</v>
+        <v>285.326</v>
       </c>
       <c r="F75">
-        <v>291.927</v>
+        <v>295.926</v>
       </c>
       <c r="G75">
         <v>67</v>
@@ -7437,28 +7437,28 @@
         <v>42</v>
       </c>
       <c r="M75">
-        <v>26.27343</v>
+        <v>26.63334</v>
       </c>
       <c r="N75">
-        <v>15.72657</v>
+        <v>15.36666</v>
       </c>
       <c r="O75">
-        <v>3.9316425</v>
+        <v>3.841664999999999</v>
       </c>
       <c r="P75">
-        <v>11.7949275</v>
+        <v>11.524995</v>
       </c>
       <c r="Q75">
-        <v>23.6949275</v>
+        <v>23.424995</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1659812679563265</v>
+        <v>0.1702219619561969</v>
       </c>
       <c r="T75">
-        <v>2.342556605745217</v>
+        <v>2.425215625002282</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.598573159271553</v>
+        <v>1.576970819281397</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0942077101086112</v>
+        <v>0.09432547786901424</v>
       </c>
       <c r="C76">
-        <v>72.52184159288652</v>
+        <v>68.15243519108822</v>
       </c>
       <c r="D76">
-        <v>301.4478415928866</v>
+        <v>301.0774351910882</v>
       </c>
       <c r="E76">
-        <v>285.326</v>
+        <v>289.325</v>
       </c>
       <c r="F76">
-        <v>295.926</v>
+        <v>299.925</v>
       </c>
       <c r="G76">
         <v>67</v>
@@ -7519,28 +7519,28 @@
         <v>42</v>
       </c>
       <c r="M76">
-        <v>26.63334</v>
+        <v>26.99325</v>
       </c>
       <c r="N76">
-        <v>15.36666</v>
+        <v>15.00675</v>
       </c>
       <c r="O76">
-        <v>3.841664999999999</v>
+        <v>3.7516875</v>
       </c>
       <c r="P76">
-        <v>11.524995</v>
+        <v>11.2550625</v>
       </c>
       <c r="Q76">
-        <v>23.424995</v>
+        <v>23.1550625</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1702219619561969</v>
+        <v>0.1748019114760569</v>
       </c>
       <c r="T76">
-        <v>2.425215625002282</v>
+        <v>2.514487365799912</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.576970819281397</v>
+        <v>1.555944541690978</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09432547786901424</v>
+        <v>0.09444324562941728</v>
       </c>
       <c r="C77">
-        <v>68.15243519108822</v>
+        <v>63.7839379516974</v>
       </c>
       <c r="D77">
-        <v>301.0774351910882</v>
+        <v>300.7079379516974</v>
       </c>
       <c r="E77">
-        <v>289.325</v>
+        <v>293.324</v>
       </c>
       <c r="F77">
-        <v>299.925</v>
+        <v>303.924</v>
       </c>
       <c r="G77">
         <v>67</v>
@@ -7601,28 +7601,28 @@
         <v>42</v>
       </c>
       <c r="M77">
-        <v>26.99325</v>
+        <v>27.35316</v>
       </c>
       <c r="N77">
-        <v>15.00675</v>
+        <v>14.64684</v>
       </c>
       <c r="O77">
-        <v>3.7516875</v>
+        <v>3.661709999999999</v>
       </c>
       <c r="P77">
-        <v>11.2550625</v>
+        <v>10.98513</v>
       </c>
       <c r="Q77">
-        <v>23.1550625</v>
+        <v>22.88513</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1748019114760569</v>
+        <v>0.1797635234559053</v>
       </c>
       <c r="T77">
-        <v>2.514487365799912</v>
+        <v>2.611198418330678</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.555944541690978</v>
+        <v>1.535471587195044</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09444324562941728</v>
+        <v>0.0945610133898203</v>
       </c>
       <c r="C78">
-        <v>63.7839379516974</v>
+        <v>59.41634653150879</v>
       </c>
       <c r="D78">
-        <v>300.7079379516974</v>
+        <v>300.3393465315089</v>
       </c>
       <c r="E78">
-        <v>293.324</v>
+        <v>297.323</v>
       </c>
       <c r="F78">
-        <v>303.924</v>
+        <v>307.9230000000001</v>
       </c>
       <c r="G78">
         <v>67</v>
@@ -7683,28 +7683,28 @@
         <v>42</v>
       </c>
       <c r="M78">
-        <v>27.35316</v>
+        <v>27.71307000000001</v>
       </c>
       <c r="N78">
-        <v>14.64684</v>
+        <v>14.28692999999999</v>
       </c>
       <c r="O78">
-        <v>3.661709999999999</v>
+        <v>3.571732499999999</v>
       </c>
       <c r="P78">
-        <v>10.98513</v>
+        <v>10.7151975</v>
       </c>
       <c r="Q78">
-        <v>22.88513</v>
+        <v>22.61519749999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1797635234559053</v>
+        <v>0.1851565799557404</v>
       </c>
       <c r="T78">
-        <v>2.611198418330678</v>
+        <v>2.716319127603249</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.535471587195044</v>
+        <v>1.515530397750953</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0945610133898203</v>
+        <v>0.1309168830224481</v>
       </c>
       <c r="C79">
-        <v>59.41634653150879</v>
+        <v>-27.03179774614307</v>
       </c>
       <c r="D79">
-        <v>300.3393465315089</v>
+        <v>217.890202253857</v>
       </c>
       <c r="E79">
-        <v>297.323</v>
+        <v>301.322</v>
       </c>
       <c r="F79">
-        <v>307.9230000000001</v>
+        <v>311.922</v>
       </c>
       <c r="G79">
         <v>67</v>
@@ -7765,45 +7765,45 @@
         <v>42</v>
       </c>
       <c r="M79">
-        <v>27.71307000000001</v>
+        <v>45.79014960000001</v>
       </c>
       <c r="N79">
-        <v>14.28692999999999</v>
+        <v>-3.790149600000007</v>
       </c>
       <c r="O79">
-        <v>3.571732499999999</v>
+        <v>-0.9475374000000016</v>
       </c>
       <c r="P79">
-        <v>10.7151975</v>
+        <v>-2.842612200000005</v>
       </c>
       <c r="Q79">
-        <v>22.61519749999999</v>
+        <v>9.057387799999995</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1851565799557404</v>
+        <v>0.1939520325612881</v>
       </c>
       <c r="T79">
-        <v>2.716319127603249</v>
+        <v>2.887758869852699</v>
       </c>
       <c r="U79">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.25</v>
+        <v>0.229306959940572</v>
       </c>
       <c r="W79">
-        <v>0.0675</v>
+        <v>0.1131377382807241</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y79">
-        <v>1.515530397750953</v>
+        <v>0.9172278397622879</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1309168830224481</v>
+        <v>0.1319268830224481</v>
       </c>
       <c r="C80">
-        <v>-27.03179774614307</v>
+        <v>-32.67994301401063</v>
       </c>
       <c r="D80">
-        <v>217.890202253857</v>
+        <v>216.2410569859894</v>
       </c>
       <c r="E80">
-        <v>301.322</v>
+        <v>305.321</v>
       </c>
       <c r="F80">
-        <v>311.922</v>
+        <v>315.921</v>
       </c>
       <c r="G80">
         <v>67</v>
@@ -7847,37 +7847,37 @@
         <v>42</v>
       </c>
       <c r="M80">
-        <v>45.79014960000001</v>
+        <v>46.37720280000001</v>
       </c>
       <c r="N80">
-        <v>-3.790149600000007</v>
+        <v>-4.377202800000013</v>
       </c>
       <c r="O80">
-        <v>-0.9475374000000016</v>
+        <v>-1.094300700000003</v>
       </c>
       <c r="P80">
-        <v>-2.842612200000005</v>
+        <v>-3.28290210000001</v>
       </c>
       <c r="Q80">
-        <v>9.057387799999995</v>
+        <v>8.61709789999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1939520325612881</v>
+        <v>0.2010068912546828</v>
       </c>
       <c r="T80">
-        <v>2.887758869852699</v>
+        <v>3.025271196988542</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.229306959940572</v>
+        <v>0.2264043401944888</v>
       </c>
       <c r="W80">
-        <v>0.1131377382807241</v>
+        <v>0.1135638428594491</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.9172278397622879</v>
+        <v>0.9056173607779551</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1319268830224481</v>
+        <v>0.1329368830224481</v>
       </c>
       <c r="C81">
-        <v>-32.67994301401063</v>
+        <v>-38.30331203884708</v>
       </c>
       <c r="D81">
-        <v>216.2410569859894</v>
+        <v>214.616687961153</v>
       </c>
       <c r="E81">
-        <v>305.321</v>
+        <v>309.3200000000001</v>
       </c>
       <c r="F81">
-        <v>315.921</v>
+        <v>319.9200000000001</v>
       </c>
       <c r="G81">
         <v>67</v>
@@ -7929,37 +7929,37 @@
         <v>42</v>
       </c>
       <c r="M81">
-        <v>46.37720280000001</v>
+        <v>46.96425600000001</v>
       </c>
       <c r="N81">
-        <v>-4.377202800000013</v>
+        <v>-4.964256000000013</v>
       </c>
       <c r="O81">
-        <v>-1.094300700000003</v>
+        <v>-1.241064000000003</v>
       </c>
       <c r="P81">
-        <v>-3.28290210000001</v>
+        <v>-3.72319200000001</v>
       </c>
       <c r="Q81">
-        <v>8.61709789999999</v>
+        <v>8.176807999999991</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2010068912546828</v>
+        <v>0.2087672358174169</v>
       </c>
       <c r="T81">
-        <v>3.025271196988542</v>
+        <v>3.176534756837969</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2264043401944888</v>
+        <v>0.2235742859420577</v>
       </c>
       <c r="W81">
-        <v>0.1135638428594491</v>
+        <v>0.1139792948237059</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.9056173607779551</v>
+        <v>0.8942971437682307</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1329368830224481</v>
+        <v>0.1339468830224481</v>
       </c>
       <c r="C82">
-        <v>-38.30331203884708</v>
+        <v>-43.90245900351414</v>
       </c>
       <c r="D82">
-        <v>214.616687961153</v>
+        <v>213.0165409964859</v>
       </c>
       <c r="E82">
-        <v>309.3200000000001</v>
+        <v>313.319</v>
       </c>
       <c r="F82">
-        <v>319.9200000000001</v>
+        <v>323.919</v>
       </c>
       <c r="G82">
         <v>67</v>
@@ -8011,37 +8011,37 @@
         <v>42</v>
       </c>
       <c r="M82">
-        <v>46.96425600000001</v>
+        <v>47.55130920000001</v>
       </c>
       <c r="N82">
-        <v>-4.964256000000013</v>
+        <v>-5.551309200000013</v>
       </c>
       <c r="O82">
-        <v>-1.241064000000003</v>
+        <v>-1.387827300000003</v>
       </c>
       <c r="P82">
-        <v>-3.72319200000001</v>
+        <v>-4.16348190000001</v>
       </c>
       <c r="Q82">
-        <v>8.176807999999991</v>
+        <v>7.736518099999991</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2087672358174169</v>
+        <v>0.2173444587551757</v>
       </c>
       <c r="T82">
-        <v>3.176534756837969</v>
+        <v>3.343720796671546</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2235742859420577</v>
+        <v>0.2208141095724026</v>
       </c>
       <c r="W82">
-        <v>0.1139792948237059</v>
+        <v>0.1143844887147713</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8942971437682307</v>
+        <v>0.8832564382896105</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1339468830224481</v>
+        <v>0.1349568830224481</v>
       </c>
       <c r="C83">
-        <v>-43.90245900351414</v>
+        <v>-49.47792168560051</v>
       </c>
       <c r="D83">
-        <v>213.0165409964859</v>
+        <v>211.4400783143996</v>
       </c>
       <c r="E83">
-        <v>313.319</v>
+        <v>317.318</v>
       </c>
       <c r="F83">
-        <v>323.919</v>
+        <v>327.9180000000001</v>
       </c>
       <c r="G83">
         <v>67</v>
@@ -8093,37 +8093,37 @@
         <v>42</v>
       </c>
       <c r="M83">
-        <v>47.55130920000001</v>
+        <v>48.13836240000001</v>
       </c>
       <c r="N83">
-        <v>-5.551309200000013</v>
+        <v>-6.138362400000013</v>
       </c>
       <c r="O83">
-        <v>-1.387827300000003</v>
+        <v>-1.534590600000003</v>
       </c>
       <c r="P83">
-        <v>-4.16348190000001</v>
+        <v>-4.603771800000009</v>
       </c>
       <c r="Q83">
-        <v>7.736518099999991</v>
+        <v>7.296228199999991</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2173444587551757</v>
+        <v>0.2268747064637966</v>
       </c>
       <c r="T83">
-        <v>3.343720796671546</v>
+        <v>3.529483063153299</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2208141095724026</v>
+        <v>0.2181212545776172</v>
       </c>
       <c r="W83">
-        <v>0.1143844887147713</v>
+        <v>0.1147797998280058</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8832564382896105</v>
+        <v>0.8724850183104689</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1349568830224481</v>
+        <v>0.1359668830224481</v>
       </c>
       <c r="C84">
-        <v>-49.47792168560051</v>
+        <v>-55.03022206001231</v>
       </c>
       <c r="D84">
-        <v>211.4400783143996</v>
+        <v>209.8867779399877</v>
       </c>
       <c r="E84">
-        <v>317.318</v>
+        <v>321.317</v>
       </c>
       <c r="F84">
-        <v>327.9180000000001</v>
+        <v>331.917</v>
       </c>
       <c r="G84">
         <v>67</v>
@@ -8175,37 +8175,37 @@
         <v>42</v>
       </c>
       <c r="M84">
-        <v>48.13836240000001</v>
+        <v>48.72541560000001</v>
       </c>
       <c r="N84">
-        <v>-6.138362400000013</v>
+        <v>-6.725415600000012</v>
       </c>
       <c r="O84">
-        <v>-1.534590600000003</v>
+        <v>-1.681353900000003</v>
       </c>
       <c r="P84">
-        <v>-4.603771800000009</v>
+        <v>-5.044061700000009</v>
       </c>
       <c r="Q84">
-        <v>7.296228199999991</v>
+        <v>6.855938299999991</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2268747064637966</v>
+        <v>0.2375261597851964</v>
       </c>
       <c r="T84">
-        <v>3.529483063153299</v>
+        <v>3.737099713927023</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2181212545776172</v>
+        <v>0.2154932876549953</v>
       </c>
       <c r="W84">
-        <v>0.1147797998280058</v>
+        <v>0.1151655853722467</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8724850183104689</v>
+        <v>0.8619731506199814</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1359668830224481</v>
+        <v>0.1369768830224481</v>
       </c>
       <c r="C85">
-        <v>-55.03022206001231</v>
+        <v>-60.55986687519498</v>
       </c>
       <c r="D85">
-        <v>209.8867779399877</v>
+        <v>208.3561331248051</v>
       </c>
       <c r="E85">
-        <v>321.317</v>
+        <v>325.316</v>
       </c>
       <c r="F85">
-        <v>331.917</v>
+        <v>335.9160000000001</v>
       </c>
       <c r="G85">
         <v>67</v>
@@ -8257,37 +8257,37 @@
         <v>42</v>
       </c>
       <c r="M85">
-        <v>48.72541560000001</v>
+        <v>49.31246880000001</v>
       </c>
       <c r="N85">
-        <v>-6.725415600000012</v>
+        <v>-7.312468800000012</v>
       </c>
       <c r="O85">
-        <v>-1.681353900000003</v>
+        <v>-1.828117200000003</v>
       </c>
       <c r="P85">
-        <v>-5.044061700000009</v>
+        <v>-5.484351600000009</v>
       </c>
       <c r="Q85">
-        <v>6.855938299999991</v>
+        <v>6.415648399999991</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2375261597851964</v>
+        <v>0.2495090447717712</v>
       </c>
       <c r="T85">
-        <v>3.737099713927023</v>
+        <v>3.970668446047461</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2154932876549953</v>
+        <v>0.2129278913733882</v>
       </c>
       <c r="W85">
-        <v>0.1151655853722467</v>
+        <v>0.1155421855463866</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8619731506199814</v>
+        <v>0.851711565493553</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1369768830224481</v>
+        <v>0.1379868830224481</v>
       </c>
       <c r="C86">
-        <v>-60.55986687519493</v>
+        <v>-66.06734820432507</v>
       </c>
       <c r="D86">
-        <v>208.3561331248051</v>
+        <v>206.8476517956749</v>
       </c>
       <c r="E86">
-        <v>325.316</v>
+        <v>329.315</v>
       </c>
       <c r="F86">
-        <v>335.916</v>
+        <v>339.915</v>
       </c>
       <c r="G86">
         <v>67</v>
@@ -8339,37 +8339,37 @@
         <v>42</v>
       </c>
       <c r="M86">
-        <v>49.3124688</v>
+        <v>49.899522</v>
       </c>
       <c r="N86">
-        <v>-7.312468800000005</v>
+        <v>-7.899522000000005</v>
       </c>
       <c r="O86">
-        <v>-1.828117200000001</v>
+        <v>-1.974880500000001</v>
       </c>
       <c r="P86">
-        <v>-5.484351600000004</v>
+        <v>-5.924641500000003</v>
       </c>
       <c r="Q86">
-        <v>6.415648399999997</v>
+        <v>5.975358499999997</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.249509044771771</v>
+        <v>0.2630896477565558</v>
       </c>
       <c r="T86">
-        <v>3.970668446047459</v>
+        <v>4.235379675783957</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2129278913733883</v>
+        <v>0.2104228573572308</v>
       </c>
       <c r="W86">
-        <v>0.1155421855463866</v>
+        <v>0.1159099245399585</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8517115654935532</v>
+        <v>0.8416914294289231</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1379868830224481</v>
+        <v>0.1389968830224481</v>
       </c>
       <c r="C87">
-        <v>-66.06734820432507</v>
+        <v>-71.55314397273071</v>
       </c>
       <c r="D87">
-        <v>206.8476517956749</v>
+        <v>205.3608560272693</v>
       </c>
       <c r="E87">
-        <v>329.315</v>
+        <v>333.314</v>
       </c>
       <c r="F87">
-        <v>339.915</v>
+        <v>343.914</v>
       </c>
       <c r="G87">
         <v>67</v>
@@ -8421,37 +8421,37 @@
         <v>42</v>
       </c>
       <c r="M87">
-        <v>49.899522</v>
+        <v>50.48657520000001</v>
       </c>
       <c r="N87">
-        <v>-7.899522000000005</v>
+        <v>-8.486575200000011</v>
       </c>
       <c r="O87">
-        <v>-1.974880500000001</v>
+        <v>-2.121643800000003</v>
       </c>
       <c r="P87">
-        <v>-5.924641500000003</v>
+        <v>-6.364931400000009</v>
       </c>
       <c r="Q87">
-        <v>5.975358499999997</v>
+        <v>5.535068599999992</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2630896477565558</v>
+        <v>0.278610336882024</v>
       </c>
       <c r="T87">
-        <v>4.235379675783957</v>
+        <v>4.537906795482811</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2104228573572308</v>
+        <v>0.2079760799461002</v>
       </c>
       <c r="W87">
-        <v>0.1159099245399585</v>
+        <v>0.1162691114639125</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8416914294289231</v>
+        <v>0.8319043197844006</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1389968830224481</v>
+        <v>0.1400068830224481</v>
       </c>
       <c r="C88">
-        <v>-71.55314397273071</v>
+        <v>-77.01771846272754</v>
       </c>
       <c r="D88">
-        <v>205.3608560272693</v>
+        <v>203.8952815372724</v>
       </c>
       <c r="E88">
-        <v>333.314</v>
+        <v>337.313</v>
       </c>
       <c r="F88">
-        <v>343.914</v>
+        <v>347.913</v>
       </c>
       <c r="G88">
         <v>67</v>
@@ -8503,37 +8503,37 @@
         <v>42</v>
       </c>
       <c r="M88">
-        <v>50.48657520000001</v>
+        <v>51.0736284</v>
       </c>
       <c r="N88">
-        <v>-8.486575200000011</v>
+        <v>-9.073628400000004</v>
       </c>
       <c r="O88">
-        <v>-2.121643800000003</v>
+        <v>-2.268407100000001</v>
       </c>
       <c r="P88">
-        <v>-6.364931400000009</v>
+        <v>-6.805221300000003</v>
       </c>
       <c r="Q88">
-        <v>5.535068599999992</v>
+        <v>5.094778699999997</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.278610336882024</v>
+        <v>0.2965188243344875</v>
       </c>
       <c r="T88">
-        <v>4.537906795482811</v>
+        <v>4.886976548981488</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2079760799461002</v>
+        <v>0.2055855502915473</v>
       </c>
       <c r="W88">
-        <v>0.1162691114639125</v>
+        <v>0.1166200412172009</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8319043197844006</v>
+        <v>0.8223422011661893</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1400068830224481</v>
+        <v>0.1410168830224481</v>
       </c>
       <c r="C89">
-        <v>-77.01771846272754</v>
+        <v>-82.46152279699186</v>
       </c>
       <c r="D89">
-        <v>203.8952815372724</v>
+        <v>202.4504772030082</v>
       </c>
       <c r="E89">
-        <v>337.313</v>
+        <v>341.312</v>
       </c>
       <c r="F89">
-        <v>347.913</v>
+        <v>351.912</v>
       </c>
       <c r="G89">
         <v>67</v>
@@ -8585,37 +8585,37 @@
         <v>42</v>
       </c>
       <c r="M89">
-        <v>51.0736284</v>
+        <v>51.66068160000001</v>
       </c>
       <c r="N89">
-        <v>-9.073628400000004</v>
+        <v>-9.660681600000011</v>
       </c>
       <c r="O89">
-        <v>-2.268407100000001</v>
+        <v>-2.415170400000003</v>
       </c>
       <c r="P89">
-        <v>-6.805221300000003</v>
+        <v>-7.245511200000008</v>
       </c>
       <c r="Q89">
-        <v>5.094778699999997</v>
+        <v>4.654488799999992</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2965188243344875</v>
+        <v>0.3174120596956948</v>
       </c>
       <c r="T89">
-        <v>4.886976548981488</v>
+        <v>5.294224594729947</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2055855502915473</v>
+        <v>0.2032493508564161</v>
       </c>
       <c r="W89">
-        <v>0.1166200412172009</v>
+        <v>0.1169629952942781</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8223422011661893</v>
+        <v>0.8129974034256643</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1410168830224481</v>
+        <v>0.1420268830224481</v>
       </c>
       <c r="C90">
-        <v>-82.46152279699186</v>
+        <v>-87.8849954015264</v>
       </c>
       <c r="D90">
-        <v>202.4504772030082</v>
+        <v>201.0260045984737</v>
       </c>
       <c r="E90">
-        <v>341.312</v>
+        <v>345.311</v>
       </c>
       <c r="F90">
-        <v>351.912</v>
+        <v>355.9110000000001</v>
       </c>
       <c r="G90">
         <v>67</v>
@@ -8667,37 +8667,37 @@
         <v>42</v>
       </c>
       <c r="M90">
-        <v>51.66068160000001</v>
+        <v>52.24773480000001</v>
       </c>
       <c r="N90">
-        <v>-9.660681600000011</v>
+        <v>-10.24773480000001</v>
       </c>
       <c r="O90">
-        <v>-2.415170400000003</v>
+        <v>-2.561933700000003</v>
       </c>
       <c r="P90">
-        <v>-7.245511200000008</v>
+        <v>-7.685801100000008</v>
       </c>
       <c r="Q90">
-        <v>4.654488799999992</v>
+        <v>4.214198899999992</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3174120596956948</v>
+        <v>0.3421040651225761</v>
       </c>
       <c r="T90">
-        <v>5.294224594729947</v>
+        <v>5.775517739705396</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2032493508564161</v>
+        <v>0.2009656502849957</v>
       </c>
       <c r="W90">
-        <v>0.1169629952942781</v>
+        <v>0.1172982425381627</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8129974034256643</v>
+        <v>0.8038626011399826</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1420268830224481</v>
+        <v>0.1935460973076392</v>
       </c>
       <c r="C91">
-        <v>-87.8849954015264</v>
+        <v>-144.9779819596342</v>
       </c>
       <c r="D91">
-        <v>201.0260045984737</v>
+        <v>147.9320180403658</v>
       </c>
       <c r="E91">
-        <v>345.311</v>
+        <v>349.31</v>
       </c>
       <c r="F91">
-        <v>355.9110000000001</v>
+        <v>359.91</v>
       </c>
       <c r="G91">
         <v>67</v>
@@ -8749,45 +8749,45 @@
         <v>42</v>
       </c>
       <c r="M91">
-        <v>52.24773480000001</v>
+        <v>72.26992800000001</v>
       </c>
       <c r="N91">
-        <v>-10.24773480000001</v>
+        <v>-30.26992800000001</v>
       </c>
       <c r="O91">
-        <v>-2.561933700000003</v>
+        <v>-7.567482000000002</v>
       </c>
       <c r="P91">
-        <v>-7.685801100000008</v>
+        <v>-22.70244600000001</v>
       </c>
       <c r="Q91">
-        <v>4.214198899999992</v>
+        <v>-10.80244600000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3421040651225761</v>
+        <v>0.3908266144867452</v>
       </c>
       <c r="T91">
-        <v>5.775517739705396</v>
+        <v>6.725210914046493</v>
       </c>
       <c r="U91">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.2009656502849957</v>
+        <v>0.1452886461987343</v>
       </c>
       <c r="W91">
-        <v>0.1172982425381627</v>
+        <v>0.1716260398432942</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.8038626011399826</v>
+        <v>0.5811545847949371</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1935460973076392</v>
+        <v>0.1950960973076393</v>
       </c>
       <c r="C92">
-        <v>-144.9779819596342</v>
+        <v>-150.1432017915757</v>
       </c>
       <c r="D92">
-        <v>147.9320180403658</v>
+        <v>146.7657982084243</v>
       </c>
       <c r="E92">
-        <v>349.31</v>
+        <v>353.309</v>
       </c>
       <c r="F92">
-        <v>359.91</v>
+        <v>363.909</v>
       </c>
       <c r="G92">
         <v>67</v>
@@ -8831,37 +8831,37 @@
         <v>42</v>
       </c>
       <c r="M92">
-        <v>72.26992800000001</v>
+        <v>73.07292720000001</v>
       </c>
       <c r="N92">
-        <v>-30.26992800000001</v>
+        <v>-31.07292720000001</v>
       </c>
       <c r="O92">
-        <v>-7.567482000000002</v>
+        <v>-7.768231800000002</v>
       </c>
       <c r="P92">
-        <v>-22.70244600000001</v>
+        <v>-23.30469540000001</v>
       </c>
       <c r="Q92">
-        <v>-10.80244600000001</v>
+        <v>-11.40469540000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3908266144867452</v>
+        <v>0.4291629049852725</v>
       </c>
       <c r="T92">
-        <v>6.725210914046493</v>
+        <v>7.472456571162772</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1452886461987343</v>
+        <v>0.1436920676690778</v>
       </c>
       <c r="W92">
-        <v>0.1716260398432942</v>
+        <v>0.1719466328120492</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5811545847949371</v>
+        <v>0.5747682706763113</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1950960973076393</v>
+        <v>0.1966460973076393</v>
       </c>
       <c r="C93">
-        <v>-150.1432017915757</v>
+        <v>-155.2901776963478</v>
       </c>
       <c r="D93">
-        <v>146.7657982084243</v>
+        <v>145.6178223036523</v>
       </c>
       <c r="E93">
-        <v>353.309</v>
+        <v>357.308</v>
       </c>
       <c r="F93">
-        <v>363.909</v>
+        <v>367.9080000000001</v>
       </c>
       <c r="G93">
         <v>67</v>
@@ -8913,37 +8913,37 @@
         <v>42</v>
       </c>
       <c r="M93">
-        <v>73.07292720000001</v>
+        <v>73.87592640000001</v>
       </c>
       <c r="N93">
-        <v>-31.07292720000001</v>
+        <v>-31.87592640000001</v>
       </c>
       <c r="O93">
-        <v>-7.768231800000002</v>
+        <v>-7.968981600000003</v>
       </c>
       <c r="P93">
-        <v>-23.30469540000001</v>
+        <v>-23.90694480000001</v>
       </c>
       <c r="Q93">
-        <v>-11.40469540000001</v>
+        <v>-12.00694480000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4291629049852725</v>
+        <v>0.4770832681084317</v>
       </c>
       <c r="T93">
-        <v>7.472456571162772</v>
+        <v>8.406513642558121</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1436920676690778</v>
+        <v>0.142130197368327</v>
       </c>
       <c r="W93">
-        <v>0.1719466328120492</v>
+        <v>0.1722602563684399</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5747682706763113</v>
+        <v>0.568520789473308</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1966460973076393</v>
+        <v>0.1981960973076393</v>
       </c>
       <c r="C94">
-        <v>-155.2901776963478</v>
+        <v>-160.4193344536356</v>
       </c>
       <c r="D94">
-        <v>145.6178223036523</v>
+        <v>144.4876655463645</v>
       </c>
       <c r="E94">
-        <v>357.308</v>
+        <v>361.307</v>
       </c>
       <c r="F94">
-        <v>367.9080000000001</v>
+        <v>371.907</v>
       </c>
       <c r="G94">
         <v>67</v>
@@ -8995,37 +8995,37 @@
         <v>42</v>
       </c>
       <c r="M94">
-        <v>73.87592640000001</v>
+        <v>74.67892560000001</v>
       </c>
       <c r="N94">
-        <v>-31.87592640000001</v>
+        <v>-32.67892560000001</v>
       </c>
       <c r="O94">
-        <v>-7.968981600000003</v>
+        <v>-8.169731400000003</v>
       </c>
       <c r="P94">
-        <v>-23.90694480000001</v>
+        <v>-24.50919420000001</v>
       </c>
       <c r="Q94">
-        <v>-12.00694480000001</v>
+        <v>-12.60919420000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4770832681084317</v>
+        <v>0.5386951635524935</v>
       </c>
       <c r="T94">
-        <v>8.406513642558121</v>
+        <v>9.607444162923569</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.142130197368327</v>
+        <v>0.1406019156761944</v>
       </c>
       <c r="W94">
-        <v>0.1722602563684399</v>
+        <v>0.1725671353322202</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.568520789473308</v>
+        <v>0.5624076627047778</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1981960973076393</v>
+        <v>0.1997460973076393</v>
       </c>
       <c r="C95">
-        <v>-160.4193344536356</v>
+        <v>-165.5310837576253</v>
       </c>
       <c r="D95">
-        <v>144.4876655463645</v>
+        <v>143.3749162423748</v>
       </c>
       <c r="E95">
-        <v>361.307</v>
+        <v>365.306</v>
       </c>
       <c r="F95">
-        <v>371.907</v>
+        <v>375.9060000000001</v>
       </c>
       <c r="G95">
         <v>67</v>
@@ -9077,37 +9077,37 @@
         <v>42</v>
       </c>
       <c r="M95">
-        <v>74.67892560000001</v>
+        <v>75.48192480000002</v>
       </c>
       <c r="N95">
-        <v>-32.67892560000001</v>
+        <v>-33.48192480000002</v>
       </c>
       <c r="O95">
-        <v>-8.169731400000003</v>
+        <v>-8.370481200000004</v>
       </c>
       <c r="P95">
-        <v>-24.50919420000001</v>
+        <v>-25.11144360000001</v>
       </c>
       <c r="Q95">
-        <v>-12.60919420000001</v>
+        <v>-13.21144360000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5386951635524935</v>
+        <v>0.6208443574779091</v>
       </c>
       <c r="T95">
-        <v>9.607444162923569</v>
+        <v>11.20868485674417</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1406019156761944</v>
+        <v>0.1391061506158094</v>
       </c>
       <c r="W95">
-        <v>0.1725671353322202</v>
+        <v>0.1728674849563455</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5624076627047778</v>
+        <v>0.5564246024632375</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1997460973076393</v>
+        <v>0.2012960973076393</v>
       </c>
       <c r="C96">
-        <v>-165.5310837576253</v>
+        <v>-170.6258247170331</v>
       </c>
       <c r="D96">
-        <v>143.3749162423748</v>
+        <v>142.279175282967</v>
       </c>
       <c r="E96">
-        <v>365.306</v>
+        <v>369.3050000000001</v>
       </c>
       <c r="F96">
-        <v>375.9060000000001</v>
+        <v>379.9050000000001</v>
       </c>
       <c r="G96">
         <v>67</v>
@@ -9159,37 +9159,37 @@
         <v>42</v>
       </c>
       <c r="M96">
-        <v>75.48192480000002</v>
+        <v>76.28492400000002</v>
       </c>
       <c r="N96">
-        <v>-33.48192480000002</v>
+        <v>-34.28492400000002</v>
       </c>
       <c r="O96">
-        <v>-8.370481200000004</v>
+        <v>-8.571231000000004</v>
       </c>
       <c r="P96">
-        <v>-25.11144360000001</v>
+        <v>-25.71369300000001</v>
       </c>
       <c r="Q96">
-        <v>-13.21144360000001</v>
+        <v>-13.81369300000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6208443574779091</v>
+        <v>0.7358532289734914</v>
       </c>
       <c r="T96">
-        <v>11.20868485674417</v>
+        <v>13.45042182809301</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1391061506158094</v>
+        <v>0.1376418753461693</v>
       </c>
       <c r="W96">
-        <v>0.1728674849563455</v>
+        <v>0.1731615114304892</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5564246024632375</v>
+        <v>0.5505675013846771</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2012960973076393</v>
+        <v>0.2028460973076393</v>
       </c>
       <c r="C97">
-        <v>-170.6258247170331</v>
+        <v>-175.7039443323785</v>
       </c>
       <c r="D97">
-        <v>142.279175282967</v>
+        <v>141.2000556676215</v>
       </c>
       <c r="E97">
-        <v>369.3050000000001</v>
+        <v>373.304</v>
       </c>
       <c r="F97">
-        <v>379.9050000000001</v>
+        <v>383.9040000000001</v>
       </c>
       <c r="G97">
         <v>67</v>
@@ -9241,37 +9241,37 @@
         <v>42</v>
       </c>
       <c r="M97">
-        <v>76.28492400000002</v>
+        <v>77.08792320000002</v>
       </c>
       <c r="N97">
-        <v>-34.28492400000002</v>
+        <v>-35.08792320000002</v>
       </c>
       <c r="O97">
-        <v>-8.571231000000004</v>
+        <v>-8.771980800000005</v>
       </c>
       <c r="P97">
-        <v>-25.71369300000001</v>
+        <v>-26.31594240000002</v>
       </c>
       <c r="Q97">
-        <v>-13.81369300000001</v>
+        <v>-14.41594240000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7358532289734914</v>
+        <v>0.9083665362168645</v>
       </c>
       <c r="T97">
-        <v>13.45042182809301</v>
+        <v>16.81302728511626</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1376418753461693</v>
+        <v>0.1362081058113133</v>
       </c>
       <c r="W97">
-        <v>0.1731615114304892</v>
+        <v>0.1734494123530883</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5505675013846771</v>
+        <v>0.5448324232452534</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2028460973076393</v>
+        <v>0.2043960973076392</v>
       </c>
       <c r="C98">
-        <v>-175.7039443323785</v>
+        <v>-180.7658179517033</v>
       </c>
       <c r="D98">
-        <v>141.2000556676215</v>
+        <v>140.1371820482967</v>
       </c>
       <c r="E98">
-        <v>373.304</v>
+        <v>377.303</v>
       </c>
       <c r="F98">
-        <v>383.904</v>
+        <v>387.903</v>
       </c>
       <c r="G98">
         <v>67</v>
@@ -9323,37 +9323,37 @@
         <v>42</v>
       </c>
       <c r="M98">
-        <v>77.08792320000001</v>
+        <v>77.89092240000001</v>
       </c>
       <c r="N98">
-        <v>-35.08792320000001</v>
+        <v>-35.89092240000001</v>
       </c>
       <c r="O98">
-        <v>-8.771980800000001</v>
+        <v>-8.972730600000002</v>
       </c>
       <c r="P98">
-        <v>-26.3159424</v>
+        <v>-26.91819180000001</v>
       </c>
       <c r="Q98">
-        <v>-14.4159424</v>
+        <v>-15.01819180000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9083665362168623</v>
+        <v>1.195888714955816</v>
       </c>
       <c r="T98">
-        <v>16.81302728511622</v>
+        <v>22.41736971348829</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1362081058113134</v>
+        <v>0.1348038985349081</v>
       </c>
       <c r="W98">
-        <v>0.1734494123530883</v>
+        <v>0.1737313771741905</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5448324232452535</v>
+        <v>0.5392155941396324</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2043960973076392</v>
+        <v>0.2059460973076393</v>
       </c>
       <c r="C99">
-        <v>-180.7658179517033</v>
+        <v>-185.8118097058604</v>
       </c>
       <c r="D99">
-        <v>140.1371820482967</v>
+        <v>139.0901902941396</v>
       </c>
       <c r="E99">
-        <v>377.303</v>
+        <v>381.302</v>
       </c>
       <c r="F99">
-        <v>387.903</v>
+        <v>391.902</v>
       </c>
       <c r="G99">
         <v>67</v>
@@ -9405,37 +9405,37 @@
         <v>42</v>
       </c>
       <c r="M99">
-        <v>77.89092240000001</v>
+        <v>78.69392160000001</v>
       </c>
       <c r="N99">
-        <v>-35.89092240000001</v>
+        <v>-36.69392160000001</v>
       </c>
       <c r="O99">
-        <v>-8.972730600000002</v>
+        <v>-9.173480400000003</v>
       </c>
       <c r="P99">
-        <v>-26.91819180000001</v>
+        <v>-27.52044120000001</v>
       </c>
       <c r="Q99">
-        <v>-15.01819180000001</v>
+        <v>-15.62044120000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.195888714955816</v>
+        <v>1.770933072433725</v>
       </c>
       <c r="T99">
-        <v>22.41736971348829</v>
+        <v>33.62605457023244</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1348038985349081</v>
+        <v>0.133428348549858</v>
       </c>
       <c r="W99">
-        <v>0.1737313771741905</v>
+        <v>0.1740075876111885</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5392155941396324</v>
+        <v>0.533713394199432</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2059460973076393</v>
+        <v>0.2074960973076393</v>
       </c>
       <c r="C100">
-        <v>-185.8118097058604</v>
+        <v>-190.8422729244351</v>
       </c>
       <c r="D100">
-        <v>139.0901902941396</v>
+        <v>138.0587270755649</v>
       </c>
       <c r="E100">
-        <v>381.302</v>
+        <v>385.301</v>
       </c>
       <c r="F100">
-        <v>391.902</v>
+        <v>395.901</v>
       </c>
       <c r="G100">
         <v>67</v>
@@ -9487,37 +9487,37 @@
         <v>42</v>
       </c>
       <c r="M100">
-        <v>78.69392160000001</v>
+        <v>79.4969208</v>
       </c>
       <c r="N100">
-        <v>-36.69392160000001</v>
+        <v>-37.4969208</v>
       </c>
       <c r="O100">
-        <v>-9.173480400000003</v>
+        <v>-9.3742302</v>
       </c>
       <c r="P100">
-        <v>-27.52044120000001</v>
+        <v>-28.1226906</v>
       </c>
       <c r="Q100">
-        <v>-15.62044120000001</v>
+        <v>-16.2226906</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.770933072433725</v>
+        <v>3.496066144867449</v>
       </c>
       <c r="T100">
-        <v>33.62605457023244</v>
+        <v>67.25210914046488</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.133428348549858</v>
+        <v>0.1320805874533948</v>
       </c>
       <c r="W100">
-        <v>0.1740075876111885</v>
+        <v>0.1742782180393583</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.533713394199432</v>
+        <v>0.5283223498135792</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2074960973076393</v>
-      </c>
-      <c r="C101">
-        <v>-190.8422729244351</v>
-      </c>
-      <c r="D101">
-        <v>138.0587270755649</v>
-      </c>
-      <c r="E101">
-        <v>385.301</v>
-      </c>
-      <c r="F101">
-        <v>395.901</v>
-      </c>
-      <c r="G101">
-        <v>67</v>
-      </c>
-      <c r="H101">
-        <v>389.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>53.9</v>
-      </c>
-      <c r="K101">
-        <v>11.9</v>
-      </c>
-      <c r="L101">
-        <v>42</v>
-      </c>
-      <c r="M101">
-        <v>79.4969208</v>
-      </c>
-      <c r="N101">
-        <v>-37.4969208</v>
-      </c>
-      <c r="O101">
-        <v>-9.3742302</v>
-      </c>
-      <c r="P101">
-        <v>-28.1226906</v>
-      </c>
-      <c r="Q101">
-        <v>-16.2226906</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.496066144867449</v>
-      </c>
-      <c r="T101">
-        <v>67.25210914046488</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1320805874533948</v>
-      </c>
-      <c r="W101">
-        <v>0.1742782180393583</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5283223498135792</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
